--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -84,12 +84,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VS Code inserting 'Co-Authored-by Copilot' into commits regardless of usage</t>
+          <t>Mercedes-Benz commits to bringing back physical buttons</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -109,24 +109,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/vscode/pull/310226</t>
+          <t>https://www.drive.com.au/news/mercedes-benz-commits-to-bringing-back-phycial-buttons/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why does it take so long to release black fan versions?</t>
+          <t>DeepClaude – Claude Code agent loop with DeepSeek V4 Pro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -146,24 +146,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.noctua.at/en/expertise/blog/how-can-it-take-so-long-to-release-black-fan-versions</t>
+          <t>https://github.com/aattaran/deepclaude</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ask.com has closed</t>
+          <t>Let's Buy Spirit Air</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -183,24 +183,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.ask.com/</t>
+          <t>https://letsbuyspiritair.com/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dav2d</t>
+          <t>New statue in London, attributed to Banksy, of a suited man, blinded by a flag</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -220,24 +220,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://code.videolan.org/videolan/dav2d</t>
+          <t>https://www.smithsonianmag.com/smart-news/attributed-to-banksy-a-new-statue-of-a-suited-man-blinded-by-a-flag-and-walking-off-a-ledge-appeared-in-central-london-180988662/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NetHack 5.0.0</t>
+          <t>BYOMesh – New LoRa mesh radio offers 100x the bandwidth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -257,24 +257,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://nethack.org/v500/release.html</t>
+          <t>https://partyon.xyz/@nullagent/116499715071759135</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AI Self-preferencing in Algorithmic Hiring: Empirical Evidence and Insights</t>
+          <t>A desktop made for one</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -294,24 +294,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.00462</t>
+          <t>https://isene.org/2026/05/Audience-of-One.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>California to begin ticketing driverless cars that violate traffic laws</t>
+          <t>Agentic Coding Is a Trap</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -331,24 +331,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/clypjx3rg2go</t>
+          <t>https://larsfaye.com/articles/agentic-coding-is-a-trap</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Do_not_track</t>
+          <t>Why TUIs are back</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -368,24 +368,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://donottrack.sh/</t>
+          <t>https://wiki.alcidesfonseca.com/blog/why-tuis-are-back/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>This Month in Ladybird - April 2026</t>
+          <t>Kimi K2.6 just beat Claude, GPT-5.5, and Gemini in a coding challenge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -405,24 +405,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://ladybird.org/newsletter/2026-04-30/</t>
+          <t>https://thinkpol.ca/2026/04/30/an-open-weights-chinese-model-just-beat-claude-gpt-5-5-and-gemini-in-a-programming-challenge/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Six Years Perfecting Maps on WatchOS</t>
+          <t>Southwest Headquarters Tour</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -442,24 +442,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.david-smith.org/blog/2026/04/29/maps-on-watchos/</t>
+          <t>https://katherinemichel.github.io/blog/travel/southwest-headquarters-tour-2026.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Russia Poisons Wikipedia</t>
+          <t>Metal Gear Solid 2's source code has been leaked on 4chan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -479,24 +479,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.bettedangerous.com/p/russia-poisons-wikipedia</t>
+          <t>https://www.thegamer.com/mgs2-hd-edition-source-code-massive-leak/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>How fast is a macOS VM, and how small could it be?</t>
+          <t>Specsmaxxing – On overcoming AI psychosis, and why I write specs in YAML</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -516,24 +516,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://eclecticlight.co/2026/05/02/how-fast-is-a-macos-vm-and-how-small-could-it-be/</t>
+          <t>https://acai.sh/blog/specsmaxxing</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>America's Expanding Domestic Surveillance</t>
+          <t>The text mode lie: why modern TUIs are a nightmare for accessibility</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -553,24 +553,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/articles/americas-expanding-domestic-surveillance-08b73187</t>
+          <t>https://xogium.me/the-text-mode-lie-why-modern-tuis-are-a-nightmare-for-accessibility</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Roblox shares plummet 18% as child safety measures weigh on bookings</t>
+          <t>Utah to hold websites liable for users who mask their location with VPNs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -590,24 +590,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/05/01/roblox-rblx-stock-child-safety-earnings.html</t>
+          <t>https://www.tomshardware.com/software/vpn/utah-becomes-first-us-state-to-target-vpn-use-with-age-verification-law</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tesla owner won $10k in court for Tesla's FSD lies. Tesla is still fighting him</t>
+          <t>For thirty years I programmed with Phish on, every day</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -627,24 +627,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://electrek.co/2026/05/02/this-tesla-owner-won-10k-in-court-for-teslas-fsd-lies-tesla-is-still-fighting-him/</t>
+          <t>https://christophermeiklejohn.com/ai/personal/phish/flow/agents/2026/05/03/rift.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Open Design: Use Your Coding Agent as a Design Engine</t>
+          <t>The 'Hidden' Costs of Great Abstractions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -664,24 +664,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://github.com/nexu-io/open-design</t>
+          <t>https://jdgr.net/the-hidden-costs-of-great-abstractions</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Today, In Short</t>
+          <t>White House Considers Vetting A.I. Models Before They Are Released</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -701,24 +701,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/briefing/today-in-short.html</t>
+          <t>https://www.nytimes.com/2026/05/04/technology/trump-ai-models.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Billionaire Chris Larsen Plans to Spend $3.5 Million in NY House Race Amid Midterm Clash Over A.I.</t>
+          <t>One Issue Uniting Democrats and Republicans? Worries About A.I.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -738,34 +738,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/us/politics/alex-bores-chris-larsen-open-ai-jack-schlossberg.html</t>
+          <t>https://www.nytimes.com/2026/05/03/us/politics/democrats-republicans-ai.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spirit Airlines Shuts Down After Years of Struggle</t>
+          <t>Anthropic and Wall Street Giants Join Forces to Create New A.I. Firm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -775,34 +775,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/02/business/spirit-airlines-shutdown.html</t>
+          <t>https://www.nytimes.com/2026/05/04/business/anthropic-blackstone-goldman-sachs-artificial-intelligence-firm.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>In Permissive Amsterdam, Ads for Fossil Fuels or Meat Are Now Verboden</t>
+          <t>Inquiry Into Fed Chair Jerome Powell Could Be Resurrected, Jeanine Pirro Says</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -812,34 +812,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/climate/in-permissive-amsterdam-ads-for-fossil-fuels-or-meat-are-now-verboden.html</t>
+          <t>https://www.nytimes.com/2026/05/03/us/politics/justice-department-fed-chair-powell-inquiry-pirro.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OpenAI’s Big Reset + A.I. in the Doctor’s Office + Talkie, a pre-1930s LLM</t>
+          <t>Trump Administration Sues Minnesota to Block Climate Lawsuit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -849,71 +849,71 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/podcasts/hardfork-openai-doctors-talkie.html</t>
+          <t>https://www.nytimes.com/2026/05/04/climate/trump-minnesota-climate-lawsuit.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maryland Is First to Ban A.I.-Driven Price Increases in Grocery Stores</t>
+          <t>This Is What Should Unite the Right and the Left on A.I.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/business/surveillance-pricing-groceries-maryland.html</t>
+          <t>https://www.nytimes.com/2026/05/04/opinion/ai-national-security-risk-politics.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Meta Deal Reversal Deepens Split Between China and Silicon Valley</t>
+          <t>What Was Discussed at Google’s White House Meeting About A.I.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -923,34 +923,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/business/china-silicon-valley-manus.html</t>
+          <t>https://www.nytimes.com/2026/05/04/business/dealbook/google-ai-white-house.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stocks Sink in Broad AI Rout Sparked by China's DeepSeek</t>
+          <t>In Permissive Amsterdam, Ads for Fossil Fuels or Meat Are Now Verboden</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WSJ · Markets</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Markets</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -960,34 +960,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/articles/nikkei-may-rise-as-weak-yen-raises-earnings-hopes-776a8056?mod=rss_markets_main</t>
+          <t>https://www.nytimes.com/2026/05/01/climate/in-permissive-amsterdam-ads-for-fossil-fuels-or-meat-are-now-verboden.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Now Wanted in Silicon Valley: Ho-Hum Businesses With Thin Profit Margins</t>
+          <t>How A.I. Is Transforming China’s Entertainment Industry</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>WSJ · Markets</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Markets</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -997,34 +997,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/articles/now-wanted-in-silicon-valley-ho-hum-businesses-with-thin-profit-margins-ab07de5f?mod=rss_markets_main</t>
+          <t>https://www.nytimes.com/2026/05/03/world/asia/china-microdrama-ai-backlash.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A.I. Shakes Up China’s Entertainment Landscape</t>
+          <t>Supreme Court Temporarily Restores Access to Abortion Pill by Mail</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1034,24 +1034,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/world/asia/100000010844213/china-ai-entertainment-microdrama.html</t>
+          <t>https://www.nytimes.com/2026/05/04/us/politics/supreme-court-abortion-pill.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Public Offering</t>
+          <t>Why the A.I. Job Apocalypse (Probably) Won’t Happen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1066,29 +1066,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/02/briefing/public-offering.html</t>
+          <t>https://www.nytimes.com/2026/05/03/opinion/ai-jobs-unemployment-silicon-valley.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>After Prison, a Financial Titan Plots an Unlikely Comeback</t>
+          <t>Maryland Is First to Ban A.I.-Driven Price Increases in Grocery Stores</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1113,29 +1113,29 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/business/after-prison-a-financial-titan-plots-an-unlikely-comeback.html</t>
+          <t>https://www.nytimes.com/2026/05/01/business/surveillance-pricing-groceries-maryland.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>How Powell Just Complicated Trump’s Fed Plans</t>
+          <t>Stocks Sink in Broad AI Rout Sparked by China's DeepSeek</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>WSJ · Markets</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Markets</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1145,34 +1145,34 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/business/dealbook/powell-fed-trump-warsh.html</t>
+          <t>https://www.wsj.com/articles/nikkei-may-rise-as-weak-yen-raises-earnings-hopes-776a8056?mod=rss_markets_main</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Supreme Court Asked to Restore Access to Abortion Pill by Mail</t>
+          <t>Now Wanted in Silicon Valley: Ho-Hum Businesses With Thin Profit Margins</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>WSJ · Markets</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Markets</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1182,34 +1182,34 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/02/us/politics/supreme-court-mail-abortion-pill.html</t>
+          <t>https://www.wsj.com/articles/now-wanted-in-silicon-valley-ho-hum-businesses-with-thin-profit-margins-ab07de5f?mod=rss_markets_main</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FEMA Disaster Aid is Flowing Slowly In Trump’s Second Term</t>
+          <t>DeepSeek’s Sequel</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1219,34 +1219,34 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/climate/fema-disaster-aid-slowdowns.html</t>
+          <t>https://www.nytimes.com/2026/05/03/world/deepseek-china-ai-iran-india-elections.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Delayed Louisiana Primaries Stoke Confusion at Ballot Box</t>
+          <t>A.I. Shakes Up China’s Entertainment Landscape</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1261,29 +1261,29 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/02/us/politics/louisiana-voting-confusion-court.html</t>
+          <t>https://www.nytimes.com/video/world/asia/100000010844213/china-ai-entertainment-microdrama.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mace, Boebert and Luna Want Congress Members to Pay a Price for Sexual Abuse. Will It Work?</t>
+          <t>MAHA Awaits Robert F. Kennedy Jr.’s Definition of Ultraprocessed Foods</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1293,76 +1293,76 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/02/us/politics/boebert-mace-luna-republican-women.html</t>
+          <t>https://www.nytimes.com/2026/05/03/business/ultraprocessed-foods-rfk-maha.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Trump Is the One Without the Cards at the Poker Table</t>
+          <t>A.I. Bots Told Scientists How to Make Biological Weapons</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/opinion/trump-iran-artificial-intelligence-china.html</t>
+          <t>https://www.nytimes.com/2026/04/29/us/ai-chatbots-biological-weapons.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>There’s a 900-Year-Old Answer to Our Most Modern Problem</t>
+          <t>OpenAI’s Big Reset + A.I. in the Doctor’s Office + Talkie, a pre-1930s LLM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1372,241 +1372,241 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/opinion/ai-crimes-law.html</t>
+          <t>https://www.nytimes.com/2026/05/01/podcasts/hardfork-openai-doctors-talkie.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Spirit Airlines Should Die. Why Is Trump Trying to Save It?</t>
+          <t>Trump Administration Orders Rapid End to Hunting Regulations on Federal Lands</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/opinion/spirit-airlines-trump-bailout-auto.html</t>
+          <t>https://www.nytimes.com/2026/05/04/climate/hunting-federal-lands-burgum.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sightings</t>
+          <t>★ Crimes Against Decency Need as Much Cover-Up as Crimes Against the Law</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Simon Willison · Tech &amp; Engineering</t>
+          <t>Daring Fireball · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>long-form</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://simonwillison.net/2026/May/2/sightings/#atom-everything</t>
+          <t>https://daringfireball.net/2026/05/crimes_against_decency_need_as_much_cover-up_as_crimes_against_the_law</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>More on Apple’s Logically Elegant Tariff Refund Puzzle Solution</t>
+          <t>Quoting Anthropic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Daring Fireball · Strategy &amp; Craft</t>
+          <t>Simon Willison · Tech &amp; Engineering</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://daringfireball.net/linked/2026/05/01/tim-cooks-clever-solution-to-the-tariff-refund-puzzle</t>
+          <t>https://simonwillison.net/2026/May/3/anthropic/#atom-everything</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>View Rama's recent LinkedIn activity</t>
+          <t>‘2 Letters From Steve’</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Daring Fireball · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>long-form</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+          <t>https://davidgelphman.wordpress.com/2013/03/29/2-letters-from-steve/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The gay jailbreak technique (2025)</t>
+          <t>Vertically Aligning Roman Numerals in Code</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>Shkspr.mobi · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>long-form</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://github.com/Exocija/ZetaLib/blob/main/The%20Gay%20Jailbreak/The%20Gay%20Jailbreak.md</t>
+          <t>https://shkspr.mobi/blog/2026/05/vertically-aligning-roman-numerals-in-code/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Show HN: WhatCable, a tiny menu bar app for inspecting USB-C cables</t>
+          <t>View Rama's recent LinkedIn activity</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>social</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t/>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://github.com/darrylmorley/whatcable</t>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ti-84 Evo</t>
+          <t>VS Code inserting 'Co-Authored-by Copilot' into commits regardless of usage</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1626,24 +1626,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://education.ti.com/en/products/calculators/graphing-calculators/ti-84-evo</t>
+          <t>https://github.com/microsoft/vscode/pull/310226</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>City Learns Flock Accessed Cameras in Children's Gymnastics Room as a Sales Demo</t>
+          <t>Why does it take so long to release black fan versions?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1663,24 +1663,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.404media.co/city-learns-flock-accessed-cameras-in-childrens-gymnastics-room-as-a-sales-pitch-demo-renews-contract-anyway/</t>
+          <t>https://www.noctua.at/en/expertise/blog/how-can-it-take-so-long-to-release-black-fan-versions</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Grok 4.3</t>
+          <t>Ask.com has closed</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1700,24 +1700,24 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://docs.x.ai/developers/models/grok-4.3</t>
+          <t>https://www.ask.com/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Uber torches 2026 AI budget on Claude Code in four months</t>
+          <t>Dav2d</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1737,24 +1737,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.briefs.co/news/uber-torches-entire-2026-ai-budget-on-claude-code-in-four-months/</t>
+          <t>https://code.videolan.org/videolan/dav2d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New research suggests people can communicate and practice skills while dreaming</t>
+          <t>NetHack 5.0.0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1774,24 +1774,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.newyorker.com/culture/annals-of-inquiry/its-possible-to-learn-in-our-sleep-should-we</t>
+          <t>https://nethack.org/v500/release.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AI uses less water than the public thinks</t>
+          <t>AI Self-preferencing in Algorithmic Hiring: Empirical Evidence and Insights</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1811,24 +1811,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://californiawaterblog.com/2026/04/26/ai-water-use-distractions-and-lessons-for-california/</t>
+          <t>https://arxiv.org/abs/2509.00462</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Apple accidentally left Claude.md files Apple Support app</t>
+          <t>California to begin ticketing driverless cars that violate traffic laws</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1848,24 +1848,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://x.com/aaronp613/status/2049986504617820551</t>
+          <t>https://www.bbc.com/news/articles/clypjx3rg2go</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ask HN: Who is hiring? (May 2026)</t>
+          <t>Do_not_track</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1885,24 +1885,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=47975571</t>
+          <t>https://donottrack.sh/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Police Have Used License Plate Readers at Least 14x to Stalk Romantic Interests</t>
+          <t>This Month in Ladybird - April 2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1922,24 +1922,24 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk-romantic-interests-at-least-14-times-in-recent-years/</t>
+          <t>https://ladybird.org/newsletter/2026-04-30/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Your website is not for you</t>
+          <t>Six Years Perfecting Maps on WatchOS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1959,24 +1959,24 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://websmith.studio/blog/your-website-is-not-for-you/</t>
+          <t>https://www.david-smith.org/blog/2026/04/29/maps-on-watchos/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Spotify adds 'Verified' badges to distinguish human artists from AI</t>
+          <t>Russia Poisons Wikipedia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1996,24 +1996,24 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/c5yerr4m1yno</t>
+          <t>https://www.bettedangerous.com/p/russia-poisons-wikipedia</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>An open letter asking NHS England to keep its code open</t>
+          <t>How fast is a macOS VM, and how small could it be?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2033,24 +2033,24 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://keepthingsopen.com</t>
+          <t>https://eclecticlight.co/2026/05/02/how-fast-is-a-macos-vm-and-how-small-could-it-be/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DeepSeek V4–almost on the frontier, a fraction of the price</t>
+          <t>America's Expanding Domestic Surveillance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2070,24 +2070,24 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://simonwillison.net/2026/Apr/24/deepseek-v4/</t>
+          <t>https://www.wsj.com/articles/americas-expanding-domestic-surveillance-08b73187</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Credit cards are vulnerable to brute force kind attacks</t>
+          <t>Roblox shares plummet 18% as child safety measures weigh on bookings</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2107,39 +2107,39 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://metin.nextc.org/posts/Credit_Cards_Are_Vulnerable_To_Brute_Force_Kind_Attacks.html</t>
+          <t>https://www.cnbc.com/2026/05/01/roblox-rblx-stock-child-safety-earnings.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Today, In Short</t>
+          <t>Tesla owner won $10k in court for Tesla's FSD lies. Tesla is still fighting him</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2149,56 +2149,56 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/briefing/today-in-short.html</t>
+          <t>https://electrek.co/2026/05/02/this-tesla-owner-won-10k-in-court-for-teslas-fsd-lies-tesla-is-still-fighting-him/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Billionaire Chris Larsen Plans to Spend $3.5 Million in NY House Race Amid Midterm Clash Over A.I.</t>
+          <t>Open Design: Use Your Coding Agent as a Design Engine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/us/politics/alex-bores-chris-larsen-open-ai-jack-schlossberg.html</t>
+          <t>https://github.com/nexu-io/open-design</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Why So Many People Already Own Shares of Elon Musk’s SpaceX</t>
+          <t>Today, In Short</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2218,24 +2218,24 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/technology/elon-musk-spacex-private-company-stock.html</t>
+          <t>https://www.nytimes.com/2026/05/01/briefing/today-in-short.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OpenAI’s Big Reset + A.I. in the Doctor’s Office + Talkie, a pre-1930s LLM</t>
+          <t>Billionaire Chris Larsen Plans to Spend $3.5 Million in NY House Race Amid Midterm Clash Over A.I.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2260,19 +2260,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/podcasts/hardfork-openai-doctors-talkie.html</t>
+          <t>https://www.nytimes.com/2026/05/01/us/politics/alex-bores-chris-larsen-open-ai-jack-schlossberg.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Maryland Is First to Ban A.I.-Driven Price Increases in Grocery Stores</t>
+          <t>Spirit Airlines Shuts Down After Years of Struggle</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2292,34 +2292,34 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/business/surveillance-pricing-groceries-maryland.html</t>
+          <t>https://www.nytimes.com/2026/05/02/business/spirit-airlines-shutdown.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pentagon Makes Deals With A.I. Companies to Expand Classified Work</t>
+          <t>In Permissive Amsterdam, Ads for Fossil Fuels or Meat Are Now Verboden</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2334,29 +2334,29 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/us/politics/pentagon-ai-companies-deals.html</t>
+          <t>https://www.nytimes.com/2026/05/01/climate/in-permissive-amsterdam-ads-for-fossil-fuels-or-meat-are-now-verboden.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Spirit Airlines Shuts Down After Years of Struggle</t>
+          <t>OpenAI’s Big Reset + A.I. in the Doctor’s Office + Talkie, a pre-1930s LLM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2366,34 +2366,34 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/02/business/spirit-airlines-shutdown.html</t>
+          <t>https://www.nytimes.com/2026/05/01/podcasts/hardfork-openai-doctors-talkie.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>In Permissive Amsterdam, Ads for Fossil Fuels or Meat Are Now Verboden</t>
+          <t>Maryland Is First to Ban A.I.-Driven Price Increases in Grocery Stores</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2408,19 +2408,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/climate/in-permissive-amsterdam-ads-for-fossil-fuels-or-meat-are-now-verboden.html</t>
+          <t>https://www.nytimes.com/2026/05/01/business/surveillance-pricing-groceries-maryland.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>After Prison, a Financial Titan Plots an Unlikely Comeback</t>
+          <t>Meta Deal Reversal Deepens Split Between China and Silicon Valley</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2440,34 +2440,34 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/business/after-prison-a-financial-titan-plots-an-unlikely-comeback.html</t>
+          <t>https://www.nytimes.com/2026/04/29/business/china-silicon-valley-manus.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OpenAI’s New Model Spurs Debate Over Computing Power</t>
+          <t>Stocks Sink in Broad AI Rout Sparked by China's DeepSeek</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>WSJ · Markets</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Markets</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2477,34 +2477,34 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/business/dealbook/openai-anthropic-compute.html</t>
+          <t>https://www.wsj.com/articles/nikkei-may-rise-as-weak-yen-raises-earnings-hopes-776a8056?mod=rss_markets_main</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Meta Deal Reversal Deepens Split Between China and Silicon Valley</t>
+          <t>Now Wanted in Silicon Valley: Ho-Hum Businesses With Thin Profit Margins</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>WSJ · Markets</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Markets</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2514,34 +2514,34 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/business/china-silicon-valley-manus.html</t>
+          <t>https://www.wsj.com/articles/now-wanted-in-silicon-valley-ho-hum-businesses-with-thin-profit-margins-ab07de5f?mod=rss_markets_main</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The World’s Central Banks Are Wrestling With a Gigantic Problem</t>
+          <t>A.I. Shakes Up China’s Entertainment Landscape</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2551,24 +2551,24 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/business/iran-war-interest-rates-central-banks.html</t>
+          <t>https://www.nytimes.com/video/world/asia/100000010844213/china-ai-entertainment-microdrama.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Trump Is the One Without the Cards at the Poker Table</t>
+          <t>Public Offering</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2583,44 +2583,44 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/opinion/trump-iran-artificial-intelligence-china.html</t>
+          <t>https://www.nytimes.com/2026/05/02/briefing/public-offering.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>There’s a 900-Year-Old Answer to Our Most Modern Problem</t>
+          <t>After Prison, a Financial Titan Plots an Unlikely Comeback</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2630,29 +2630,29 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/opinion/ai-crimes-law.html</t>
+          <t>https://www.nytimes.com/2026/05/01/business/after-prison-a-financial-titan-plots-an-unlikely-comeback.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>N.I.H. Reinstates Employee Put on Leave After Criticizing Trump Research Cuts</t>
+          <t>How Powell Just Complicated Trump’s Fed Plans</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2662,34 +2662,34 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/us/politics/trump-jenna-norton-nih.html</t>
+          <t>https://www.nytimes.com/2026/04/30/business/dealbook/powell-fed-trump-warsh.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>How A.I. Data Centers Are Building a New Political Coalition</t>
+          <t>Supreme Court Asked to Restore Access to Abortion Pill by Mail</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2699,34 +2699,34 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/us/100000010828227/how-ai-data-centers-are-building-a-new-political-coalition.html</t>
+          <t>https://www.nytimes.com/2026/05/02/us/politics/supreme-court-mail-abortion-pill.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A.I. Spending Sets a Record, With No End in Sight</t>
+          <t>FEMA Disaster Aid is Flowing Slowly In Trump’s Second Term</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2736,34 +2736,34 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/technology/ai-spending-tech-data-centers.html</t>
+          <t>https://www.nytimes.com/2026/05/01/climate/fema-disaster-aid-slowdowns.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Spirit Airlines Prepares to Shut Down After Trump Administration Bailout Falls Through</t>
+          <t>Delayed Louisiana Primaries Stoke Confusion at Ballot Box</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2773,76 +2773,76 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/business/spirit-airlines-shutting-down.html</t>
+          <t>https://www.nytimes.com/2026/05/02/us/politics/louisiana-voting-confusion-court.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Spirit Airlines Should Die. Why Is Trump Trying to Save It?</t>
+          <t>Mace, Boebert and Luna Want Congress Members to Pay a Price for Sexual Abuse. Will It Work?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/opinion/spirit-airlines-trump-bailout-auto.html</t>
+          <t>https://www.nytimes.com/2026/05/02/us/politics/boebert-mace-luna-republican-women.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Forest Service Research Labs Are Closing</t>
+          <t>Trump Is the One Without the Cards at the Poker Table</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2852,34 +2852,34 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/climate/forest-service-labs-wildfire-research.html</t>
+          <t>https://www.nytimes.com/2026/05/01/opinion/trump-iran-artificial-intelligence-china.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>iNaturalist Sightings</t>
+          <t>There’s a 900-Year-Old Answer to Our Most Modern Problem</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Simon Willison · Tech &amp; Engineering</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2889,98 +2889,98 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://simonwillison.net/2026/May/1/inat-sightings/#atom-everything</t>
+          <t>https://www.nytimes.com/2026/04/30/opinion/ai-crimes-law.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Meta Solved Their Problem With Kenyan Contractors Seeing Footage of AI Glasses Wearers on the Toilet</t>
+          <t>Spirit Airlines Should Die. Why Is Trump Trying to Save It?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Daring Fireball · Strategy &amp; Craft</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/c5y7yvgy0w6o</t>
+          <t>https://www.nytimes.com/2026/04/29/opinion/spirit-airlines-trump-bailout-auto.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Talk Show: ‘Food and Beverage Director’</t>
+          <t>Sightings</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Daring Fireball · Strategy &amp; Craft</t>
+          <t>Simon Willison · Tech &amp; Engineering</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://daringfireball.net/thetalkshow/2026/04/30/ep-446</t>
+          <t>https://simonwillison.net/2026/May/2/sightings/#atom-everything</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NHS Goes To War Against Open Source</t>
+          <t>More on Apple’s Logically Elegant Tariff Refund Puzzle Solution</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Shkspr.mobi · Strategy &amp; Craft</t>
+          <t>Daring Fireball · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2995,19 +2995,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://shkspr.mobi/blog/2026/05/nhs-goes-to-war-against-open-source/</t>
+          <t>https://daringfireball.net/linked/2026/05/01/tim-cooks-clever-solution-to-the-tariff-refund-puzzle</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Claude Code refuses requests or charges extra if your commits mention "OpenClaw"</t>
+          <t>The gay jailbreak technique (2025)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3069,24 +3069,24 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://twitter.com/theo/status/2049645973350363168</t>
+          <t>https://github.com/Exocija/ZetaLib/blob/main/The%20Gay%20Jailbreak/The%20Gay%20Jailbreak.md</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Belgium stops decommissioning nuclear power plants</t>
+          <t>Show HN: WhatCable, a tiny menu bar app for inspecting USB-C cables</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://dpa-international.com/general-news/urn:newsml:dpa.com:20090101:260430-930-14717/</t>
+          <t>https://github.com/darrylmorley/whatcable</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Can I disable all data collection from my vehicle?</t>
+          <t>Ti-84 Evo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3143,24 +3143,24 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://rivian.com/support/article/can-i-disable-all-data-collection-from-my-vehicle</t>
+          <t>https://education.ti.com/en/products/calculators/graphing-calculators/ti-84-evo</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>How Mark Klein told the EFF about Room 641A [book excerpt]</t>
+          <t>City Learns Flock Accessed Cameras in Children's Gymnastics Room as a Sales Demo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3180,24 +3180,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://thereader.mitpress.mit.edu/the-whistleblower-who-uncovered-the-nsas-big-brother-machine/</t>
+          <t>https://www.404media.co/city-learns-flock-accessed-cameras-in-childrens-gymnastics-room-as-a-sales-pitch-demo-renews-contract-anyway/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mozilla's opposition to Chrome's Prompt API</t>
+          <t>Grok 4.3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3217,24 +3217,24 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://github.com/mozilla/standards-positions/issues/1213#issuecomment-4347988313</t>
+          <t>https://docs.x.ai/developers/models/grok-4.3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>For Linux kernel vulnerabilities, there is no heads-up to distributions</t>
+          <t>Uber torches 2026 AI budget on Claude Code in four months</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3254,24 +3254,24 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.openwall.com/lists/oss-security/2026/04/30/10</t>
+          <t>https://www.briefs.co/news/uber-torches-entire-2026-ai-budget-on-claude-code-in-four-months/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>How an oil refinery works</t>
+          <t>New research suggests people can communicate and practice skills while dreaming</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3291,24 +3291,24 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.construction-physics.com/p/how-an-oil-refinery-works</t>
+          <t>https://www.newyorker.com/culture/annals-of-inquiry/its-possible-to-learn-in-our-sleep-should-we</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Meta in row after workers who saw smart glasses users having sex lose jobs</t>
+          <t>AI uses less water than the public thinks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3328,24 +3328,24 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/c5y7yvgy0w6o</t>
+          <t>https://californiawaterblog.com/2026/04/26/ai-water-use-distractions-and-lessons-for-california/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Spain's parliament will act against massive IP blockages by LaLiga</t>
+          <t>Apple accidentally left Claude.md files Apple Support app</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3365,24 +3365,24 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.democrata.es/en/politics/congress-and-senate/congress-will-act-against-massive-ip-blockages-by-laliga/</t>
+          <t>https://x.com/aaronp613/status/2049986504617820551</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Shai-Hulud Themed Malware Found in the PyTorch Lightning AI Training Library</t>
+          <t>Ask HN: Who is hiring? (May 2026)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3402,24 +3402,24 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://semgrep.dev/blog/2026/malicious-dependency-in-pytorch-lightning-used-for-ai-training/</t>
+          <t>https://news.ycombinator.com/item?id=47975571</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LinkedIn is scanning browser extensions</t>
+          <t>Police Have Used License Plate Readers at Least 14x to Stalk Romantic Interests</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3439,24 +3439,24 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://404privacy.com/blog/linkedin-is-scanning-your-browser-extensions-this-is-how-they-use-the-data/</t>
+          <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk-romantic-interests-at-least-14-times-in-recent-years/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>I built a Game Boy emulator in F#</t>
+          <t>Your website is not for you</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3476,24 +3476,24 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://nickkossolapov.github.io/fame-boy/building-a-game-boy-emulator-in-fsharp/</t>
+          <t>https://websmith.studio/blog/your-website-is-not-for-you/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>U.S. Senators Vote to Ban Themselves from Trading on Prediction Markets</t>
+          <t>Spotify adds 'Verified' badges to distinguish human artists from AI</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3513,24 +3513,24 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/politics/policy/senators-vote-to-ban-themselves-from-trading-on-prediction-markets-ae4535dd</t>
+          <t>https://www.bbc.com/news/articles/c5yerr4m1yno</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Granite 4.1: IBM's 8B Model Matching 32B MoE</t>
+          <t>An open letter asking NHS England to keep its code open</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3550,24 +3550,24 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://firethering.com/granite-4-1-ibm-open-source-model-family/</t>
+          <t>https://keepthingsopen.com</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>I aggregated 28 US Government auction sites into one search</t>
+          <t>DeepSeek V4–almost on the frontier, a fraction of the price</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3587,24 +3587,24 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://bidprowl.com</t>
+          <t>https://simonwillison.net/2026/Apr/24/deepseek-v4/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GCC 16 has been released</t>
+          <t>Credit cards are vulnerable to brute force kind attacks</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3624,24 +3624,24 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://gcc.gnu.org/gcc-16/changes.html</t>
+          <t>https://metin.nextc.org/posts/Credit_Cards_Are_Vulnerable_To_Brute_Force_Kind_Attacks.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Billionaire Chris Larsen Plans to Spend $3.5 Million in NY House Race Amid Midterm Clash Over A.I.</t>
+          <t>Today, In Short</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3661,24 +3661,24 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/us/politics/alex-bores-chris-larsen-open-ai-jack-schlossberg.html</t>
+          <t>https://www.nytimes.com/2026/05/01/briefing/today-in-short.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Today, In Short</t>
+          <t>Billionaire Chris Larsen Plans to Spend $3.5 Million in NY House Race Amid Midterm Clash Over A.I.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3703,14 +3703,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/briefing/today-in-short.html</t>
+          <t>https://www.nytimes.com/2026/05/01/us/politics/alex-bores-chris-larsen-open-ai-jack-schlossberg.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3747,7 +3747,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3784,7 +3784,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3821,7 +3821,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3858,12 +3858,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>How Powell Just Complicated Trump’s Fed Plans</t>
+          <t>Spirit Airlines Shuts Down After Years of Struggle</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3883,34 +3883,34 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/business/dealbook/powell-fed-trump-warsh.html</t>
+          <t>https://www.nytimes.com/2026/05/02/business/spirit-airlines-shutdown.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Meta Deal Reversal Deepens Split Between China and Silicon Valley</t>
+          <t>In Permissive Amsterdam, Ads for Fossil Fuels or Meat Are Now Verboden</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3920,34 +3920,34 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/business/china-silicon-valley-manus.html</t>
+          <t>https://www.nytimes.com/2026/05/01/climate/in-permissive-amsterdam-ads-for-fossil-fuels-or-meat-are-now-verboden.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Fed Meeting Underscores Tough Task Ahead for Warsh</t>
+          <t>After Prison, a Financial Titan Plots an Unlikely Comeback</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NYT · Economy</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3957,34 +3957,34 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/business/economy/what-to-watch-at-the-federal-reserves-april-meeting.html</t>
+          <t>https://www.nytimes.com/2026/05/01/business/after-prison-a-financial-titan-plots-an-unlikely-comeback.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>United Airlines CEO, Rebuffed by American, Says He’s Skeptical of Other Deals</t>
+          <t>OpenAI’s New Model Spurs Debate Over Computing Power</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3994,34 +3994,34 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/business/united-airlines-american-scott-kirby.html</t>
+          <t>https://www.nytimes.com/2026/05/01/business/dealbook/openai-anthropic-compute.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>In Permissive Amsterdam, Ads for Fossil Fuels or Meat Are Now Verboden</t>
+          <t>Meta Deal Reversal Deepens Split Between China and Silicon Valley</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4031,34 +4031,34 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/climate/in-permissive-amsterdam-ads-for-fossil-fuels-or-meat-are-now-verboden.html</t>
+          <t>https://www.nytimes.com/2026/04/29/business/china-silicon-valley-manus.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Musk says he ‘was a fool’ to provide OpenAI’s early funding.</t>
+          <t>The World’s Central Banks Are Wrestling With a Gigantic Problem</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4068,76 +4068,76 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/live/2026/04/30/technology/openai-trial-sam-altman-elon-musk/musk-says-he-was-a-fool-to-provide-openais-early-funding</t>
+          <t>https://www.nytimes.com/2026/05/01/business/iran-war-interest-rates-central-banks.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>A.I. Spending Sets a Record, With No End in Sight</t>
+          <t>Trump Is the One Without the Cards at the Poker Table</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/technology/ai-spending-tech-data-centers.html</t>
+          <t>https://www.nytimes.com/2026/05/01/opinion/trump-iran-artificial-intelligence-china.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>How A.I. Data Centers Are Building a New Political Coalition</t>
+          <t>There’s a 900-Year-Old Answer to Our Most Modern Problem</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4147,34 +4147,34 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/us/100000010828227/how-ai-data-centers-are-building-a-new-political-coalition.html</t>
+          <t>https://www.nytimes.com/2026/04/30/opinion/ai-crimes-law.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Trump Is the One Without the Cards at the Poker Table</t>
+          <t>N.I.H. Reinstates Employee Put on Leave After Criticizing Trump Research Cuts</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4184,19 +4184,19 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/opinion/trump-iran-artificial-intelligence-china.html</t>
+          <t>https://www.nytimes.com/2026/05/01/us/politics/trump-jenna-norton-nih.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Musk vs. Altman: What Is This Really About?</t>
+          <t>How A.I. Data Centers Are Building a New Political Coalition</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4221,66 +4221,66 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/technology/100000010865043/musk-vs-altman-what-is-this-really-about.html</t>
+          <t>https://www.nytimes.com/video/us/100000010828227/how-ai-data-centers-are-building-a-new-political-coalition.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>There’s a 900-Year-Old Answer to Our Most Modern Problem</t>
+          <t>A.I. Spending Sets a Record, With No End in Sight</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/opinion/ai-crimes-law.html</t>
+          <t>https://www.nytimes.com/2026/04/29/technology/ai-spending-tech-data-centers.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>N.I.H. Reinstates Employee Put on Leave After Criticizing Trump Research Cuts</t>
+          <t>Spirit Airlines Prepares to Shut Down After Trump Administration Bailout Falls Through</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4295,14 +4295,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/01/us/politics/trump-jenna-norton-nih.html</t>
+          <t>https://www.nytimes.com/2026/05/01/business/spirit-airlines-shutting-down.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4339,222 +4339,222 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Why Are We Still Driving?</t>
+          <t>Forest Service Research Labs Are Closing</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/opinion/waymo-self-driving-cars-andrew-miller.html</t>
+          <t>https://www.nytimes.com/2026/04/30/climate/forest-service-labs-wildfire-research.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Audit Yourself to Get More From GenAI</t>
+          <t>iNaturalist Sightings</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MIT Sloan Review · Strategy &amp; Craft</t>
+          <t>Simon Willison · Tech &amp; Engineering</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://sloanreview.mit.edu/article/audit-yourself-to-get-more-from-genai/</t>
+          <t>https://simonwillison.net/2026/May/1/inat-sightings/#atom-everything</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Our evaluation of OpenAI's GPT-5.5 cyber capabilities</t>
+          <t>Meta Solved Their Problem With Kenyan Contractors Seeing Footage of AI Glasses Wearers on the Toilet</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Simon Willison · Tech &amp; Engineering</t>
+          <t>Daring Fireball · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>long-form</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://simonwillison.net/2026/Apr/30/gpt-55-cyber-capabilities/#atom-everything</t>
+          <t>https://www.bbc.com/news/articles/c5y7yvgy0w6o</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>The Zig project's rationale for their firm anti-AI contribution policy</t>
+          <t>The Talk Show: ‘Food and Beverage Director’</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Simon Willison · Tech &amp; Engineering</t>
+          <t>Daring Fireball · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>long-form</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://simonwillison.net/2026/Apr/30/zig-anti-ai/#atom-everything</t>
+          <t>https://daringfireball.net/thetalkshow/2026/04/30/ep-446</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Anti-DDoS Firm Heaped Attacks on Brazilian ISPs</t>
+          <t>NHS Goes To War Against Open Source</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Krebs on Security · Security &amp; Privacy</t>
+          <t>Shkspr.mobi · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>long-form</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://krebsonsecurity.com/2026/04/anti-ddos-firm-heaped-attacks-on-brazilian-isps/</t>
+          <t>https://shkspr.mobi/blog/2026/05/nhs-goes-to-war-against-open-source/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>House prices and fertility</t>
+          <t>View Rama's recent LinkedIn activity</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Lemire.me · Tech &amp; Engineering</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>social</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t/>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://lemire.me/blog/2026/04/30/house-prices-and-fertility/</t>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
         </is>
       </c>
     </row>
@@ -4566,22 +4566,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>I’m Starting to Wonder What They’re Smoking Over There at MacRumors</t>
+          <t>Claude Code refuses requests or charges extra if your commits mention "OpenClaw"</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Daring Fireball · Strategy &amp; Craft</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.macrumors.com/2026/04/29/apple-questioning-iphone-magsafe/</t>
+          <t>https://twitter.com/theo/status/2049645973350363168</t>
         </is>
       </c>
     </row>
@@ -4603,22 +4603,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>New Banksy in London</t>
+          <t>Belgium stops decommissioning nuclear power plants</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Daring Fireball · Strategy &amp; Craft</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DXwf7pis6KT/</t>
+          <t>https://dpa-international.com/general-news/urn:newsml:dpa.com:20090101:260430-930-14717/</t>
         </is>
       </c>
     </row>
@@ -4640,44 +4640,44 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>View Rama's recent LinkedIn activity</t>
+          <t>Can I disable all data collection from my vehicle?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+          <t>https://rivian.com/support/article/can-i-disable-all-data-collection-from-my-vehicle</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Zed 1.0</t>
+          <t>How Mark Klein told the EFF about Room 641A [book excerpt]</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4697,24 +4697,24 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://zed.dev/blog/zed-1-0</t>
+          <t>https://thereader.mitpress.mit.edu/the-whistleblower-who-uncovered-the-nsas-big-brother-machine/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Copy Fail</t>
+          <t>Mozilla's opposition to Chrome's Prompt API</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4734,24 +4734,24 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://copy.fail/</t>
+          <t>https://github.com/mozilla/standards-positions/issues/1213#issuecomment-4347988313</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HERMES.md in commit messages causes requests to route to extra usage billing</t>
+          <t>For Linux kernel vulnerabilities, there is no heads-up to distributions</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4771,24 +4771,24 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://github.com/anthropics/claude-code/issues/53262</t>
+          <t>https://www.openwall.com/lists/oss-security/2026/04/30/10</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cursor Camp</t>
+          <t>How an oil refinery works</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4808,24 +4808,24 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://neal.fun/cursor-camp/</t>
+          <t>https://www.construction-physics.com/p/how-an-oil-refinery-works</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Where the goblins came from</t>
+          <t>Meta in row after workers who saw smart glasses users having sex lose jobs</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4845,24 +4845,24 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://openai.com/index/where-the-goblins-came-from/</t>
+          <t>https://www.bbc.com/news/articles/c5y7yvgy0w6o</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Online age verification is the hill to die on</t>
+          <t>Spain's parliament will act against massive IP blockages by LaLiga</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4882,24 +4882,24 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://x.com/GlennMeder/status/2049088498163216560</t>
+          <t>https://www.democrata.es/en/politics/congress-and-senate/congress-will-act-against-massive-ip-blockages-by-laliga/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>We need a federation of forges</t>
+          <t>Shai-Hulud Themed Malware Found in the PyTorch Lightning AI Training Library</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4919,24 +4919,24 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://blog.tangled.org/federation/</t>
+          <t>https://semgrep.dev/blog/2026/malicious-dependency-in-pytorch-lightning-used-for-ai-training/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>The Zig project's rationale for their anti-AI contribution policy</t>
+          <t>LinkedIn is scanning browser extensions</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4956,24 +4956,24 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://simonwillison.net/2026/Apr/30/zig-anti-ai/</t>
+          <t>https://404privacy.com/blog/linkedin-is-scanning-your-browser-extensions-this-is-how-they-use-the-data/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Soft launch of open-source code platform for government</t>
+          <t>I built a Game Boy emulator in F#</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4993,24 +4993,24 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.nldigitalgovernment.nl/news/soft-launch-for-government-open-source-code-platform/</t>
+          <t>https://nickkossolapov.github.io/fame-boy/building-a-game-boy-emulator-in-fsharp/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Mistral Medium 3.5</t>
+          <t>U.S. Senators Vote to Ban Themselves from Trading on Prediction Markets</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5030,24 +5030,24 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://mistral.ai/news/vibe-remote-agents-mistral-medium-3-5</t>
+          <t>https://www.wsj.com/politics/policy/senators-vote-to-ban-themselves-from-trading-on-prediction-markets-ae4535dd</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HashiCorp co-founder says GitHub 'no longer a place for serious work'</t>
+          <t>Granite 4.1: IBM's 8B Model Matching 32B MoE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5067,24 +5067,24 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/2026/04/29/mitchell_hashimoto_ghostty_quitting_github/</t>
+          <t>https://firethering.com/granite-4-1-ibm-open-source-model-family/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FastCGI: 30 years old and still the better protocol for reverse proxies</t>
+          <t>I aggregated 28 US Government auction sites into one search</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5104,24 +5104,24 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.agwa.name/blog/post/fastcgi_is_the_better_protocol_for_reverse_proxies</t>
+          <t>https://bidprowl.com</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kyoto cherry blossoms now bloom earlier than at any point in 1,200 years</t>
+          <t>GCC 16 has been released</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5141,135 +5141,135 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://jivx.com/kyoto-bloom</t>
+          <t>https://gcc.gnu.org/gcc-16/changes.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>OpenTrafficMap</t>
+          <t>Billionaire Chris Larsen Plans to Spend $3.5 Million in NY House Race Amid Midterm Clash Over A.I.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://opentrafficmap.org/</t>
+          <t>https://www.nytimes.com/2026/05/01/us/politics/alex-bores-chris-larsen-open-ai-jack-schlossberg.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Laws of UX</t>
+          <t>Today, In Short</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://lawsofux.com/</t>
+          <t>https://www.nytimes.com/2026/05/01/briefing/today-in-short.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Maryland becomes first state to ban surveillance pricing in grocery stores</t>
+          <t>Why So Many People Already Own Shares of Elon Musk’s SpaceX</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology/2026/apr/29/maryland-grocery-stores-ban-surveillance-pricing</t>
+          <t>https://www.nytimes.com/2026/05/01/technology/elon-musk-spacex-private-company-stock.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>A.I. Spending Sets a Record, With No End in Sight</t>
+          <t>OpenAI’s Big Reset + A.I. in the Doctor’s Office + Talkie, a pre-1930s LLM</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5289,24 +5289,24 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/technology/ai-spending-tech-data-centers.html</t>
+          <t>https://www.nytimes.com/2026/05/01/podcasts/hardfork-openai-doctors-talkie.html</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Meta Deal Reversal Deepens Split Between China and Silicon Valley</t>
+          <t>Maryland Is First to Ban A.I.-Driven Price Increases in Grocery Stores</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5326,34 +5326,34 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/business/china-silicon-valley-manus.html</t>
+          <t>https://www.nytimes.com/2026/05/01/business/surveillance-pricing-groceries-maryland.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>United Airlines CEO, Rebuffed by American, Says He’s Skeptical of Other Deals</t>
+          <t>Pentagon Makes Deals With A.I. Companies to Expand Classified Work</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5363,34 +5363,34 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/business/united-airlines-american-scott-kirby.html</t>
+          <t>https://www.nytimes.com/2026/05/01/us/politics/pentagon-ai-companies-deals.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Musk Says He ‘Was a Fool’ to Provide OpenAI’s Early Funding</t>
+          <t>How Powell Just Complicated Trump’s Fed Plans</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5405,71 +5405,71 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/technology/musk-openai-trial-altman.html</t>
+          <t>https://www.nytimes.com/2026/04/30/business/dealbook/powell-fed-trump-warsh.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Meta Deal Reversal Deepens Split Between China and Silicon Valley</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>There’s a 900-Year-Old Answer to Our Most Modern Problem</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>NYT · AI</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>opinion</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/opinion/ai-crimes-law.html</t>
+          <t>https://www.nytimes.com/2026/04/29/business/china-silicon-valley-manus.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Why Are We Still Driving?</t>
+          <t>Fed Meeting Underscores Tough Task Ahead for Warsh</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Economy</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5479,66 +5479,66 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/opinion/waymo-self-driving-cars-andrew-miller.html</t>
+          <t>https://www.nytimes.com/2026/04/29/business/economy/what-to-watch-at-the-federal-reserves-april-meeting.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>United Airlines CEO, Rebuffed by American, Says He’s Skeptical of Other Deals</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Fed Meeting Underscores Tough Task Ahead for Warsh</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>NYT · Economy</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/business/economy/what-to-watch-at-the-federal-reserves-april-meeting.html</t>
+          <t>https://www.nytimes.com/2026/04/29/business/united-airlines-american-scott-kirby.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>How Powell Just Complicated Trump’s Fed Plans</t>
+          <t>In Permissive Amsterdam, Ads for Fossil Fuels or Meat Are Now Verboden</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5548,108 +5548,108 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/business/dealbook/powell-fed-trump-warsh.html</t>
+          <t>https://www.nytimes.com/2026/05/01/climate/in-permissive-amsterdam-ads-for-fossil-fuels-or-meat-are-now-verboden.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Spirit Airlines Should Die. Why Is Trump Trying to Save It?</t>
+          <t>Musk says he ‘was a fool’ to provide OpenAI’s early funding.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/opinion/spirit-airlines-trump-bailout-auto.html</t>
+          <t>https://www.nytimes.com/live/2026/04/30/technology/openai-trial-sam-altman-elon-musk/musk-says-he-was-a-fool-to-provide-openais-early-funding</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>A.I. Spending Sets a Record, With No End in Sight</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Rising Fuel Prices Force Policymakers to Weigh Excruciating Choices</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>NYT · Business</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/business/bank-of-england-european-central-bank.html</t>
+          <t>https://www.nytimes.com/2026/04/29/technology/ai-spending-tech-data-centers.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>How the Fed’s rate decision affects your finances.</t>
+          <t>How A.I. Data Centers Are Building a New Political Coalition</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>NYT · Economy</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5659,24 +5659,24 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/live/2026/04/29/business/federal-reserve-interest-rates/how-the-feds-rate-decision-affects-your-finances</t>
+          <t>https://www.nytimes.com/video/us/100000010828227/how-ai-data-centers-are-building-a-new-political-coalition.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>A.I. Is Eliminating Jobs on Wall Street</t>
+          <t>Trump Is the One Without the Cards at the Poker Table</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5691,29 +5691,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/21/business/ai-job-cuts-wall-street.html</t>
+          <t>https://www.nytimes.com/2026/05/01/opinion/trump-iran-artificial-intelligence-china.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>How Good Is Google’s Gemini AI at Making Travel Plans?</t>
+          <t>Musk vs. Altman: What Is This Really About?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5733,61 +5733,61 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/travel/ai-travel-plan-gemini-vacation.html</t>
+          <t>https://www.nytimes.com/video/technology/100000010865043/musk-vs-altman-what-is-this-really-about.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Inside the Courtroom at the OpenAI Trial</t>
+          <t>There’s a 900-Year-Old Answer to Our Most Modern Problem</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/insider/times-inside-openai-musk-trial.html</t>
+          <t>https://www.nytimes.com/2026/04/30/opinion/ai-crimes-law.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Trump Administration Sues New Jersey Governor Over ICE Mask Ban</t>
+          <t>N.I.H. Reinstates Employee Put on Leave After Criticizing Trump Research Cuts</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5807,76 +5807,76 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/nyregion/new-jersey-trump-ice-mask-lawsuit.html</t>
+          <t>https://www.nytimes.com/2026/05/01/us/politics/trump-jenna-norton-nih.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Spirit Airlines Should Die. Why Is Trump Trying to Save It?</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>NYT · Opinion</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Opinion</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Silicon Valley Is Bracing for a Permanent Underclass</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>NYT · AI</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>opinion</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/opinion/ai-labor-work-force-silicon-valley.html</t>
+          <t>https://www.nytimes.com/2026/04/29/opinion/spirit-airlines-trump-bailout-auto.html</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>How A.I. Killed Student Writing (and Revived It)</t>
+          <t>Why Are We Still Driving?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5886,71 +5886,71 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/us/ai-students-cheating-homework-classrooms.html</t>
+          <t>https://www.nytimes.com/2026/04/30/opinion/waymo-self-driving-cars-andrew-miller.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ford Reports Higher Profit Thanks Partly to Tariff Refund</t>
+          <t>Audit Yourself to Get More From GenAI</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>MIT Sloan Review · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/business/ford-motor-tariff-refund-profit.html</t>
+          <t>https://sloanreview.mit.edu/article/audit-yourself-to-get-more-from-genai/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>After Supreme Court Decision, Louisiana Weighs Redrawing House Maps</t>
+          <t>Our evaluation of OpenAI's GPT-5.5 cyber capabilities</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>Simon Willison · Tech &amp; Engineering</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5960,34 +5960,34 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/us/politics/louisiana-suspend-primaries-supreme-court.html</t>
+          <t>https://simonwillison.net/2026/Apr/30/gpt-55-cyber-capabilities/#atom-everything</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Forest Service Research Labs Are Closing</t>
+          <t>The Zig project's rationale for their firm anti-AI contribution policy</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>Simon Willison · Tech &amp; Engineering</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5997,93 +5997,93 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/30/climate/forest-service-labs-wildfire-research.html</t>
+          <t>https://simonwillison.net/2026/Apr/30/zig-anti-ai/#atom-everything</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Leaders at All Levels: How Argenx Scaled to $4 Billion Without Bureaucracy</t>
+          <t>Anti-DDoS Firm Heaped Attacks on Brazilian ISPs</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MIT Sloan Review · Strategy &amp; Craft</t>
+          <t>Krebs on Security · Security &amp; Privacy</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://sloanreview.mit.edu/video/leaders-at-all-levels-how-argenx-scaled-to-4-billion-without-bureaucracy/</t>
+          <t>https://krebsonsecurity.com/2026/04/anti-ddos-firm-heaped-attacks-on-brazilian-isps/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OpenAI Trial Starts With Two Very Different Tales of a Company’s Early Years</t>
+          <t>House prices and fertility</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Daring Fireball · Strategy &amp; Craft</t>
+          <t>Lemire.me · Tech &amp; Engineering</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/28/technology/openai-trial-elon-musk-sam-altman.html?unlocked_article_code=1.elA.u75G.-STmUe_pILOO</t>
+          <t>https://lemire.me/blog/2026/04/30/house-prices-and-fertility/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Playing With Fire</t>
+          <t>I’m Starting to Wonder What They’re Smoking Over There at MacRumors</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6103,86 +6103,86 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://x.com/lifeof_jer/status/2048103471019434248?s=12</t>
+          <t>https://www.macrumors.com/2026/04/29/apple-questioning-iphone-magsafe/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LLM 0.32a0 is a major backwards-compatible refactor</t>
+          <t>New Banksy in London</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Simon Willison · Tech &amp; Engineering</t>
+          <t>Daring Fireball · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>long-form</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://simonwillison.net/2026/Apr/29/llm/#atom-everything</t>
+          <t>https://www.instagram.com/reel/DXwf7pis6KT/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Let's Get Digging!</t>
+          <t>View Rama's recent LinkedIn activity</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Shkspr.mobi · Strategy &amp; Craft</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>social</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t/>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://shkspr.mobi/blog/2026/04/lets-get-digging/</t>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>llm 0.32a1</t>
+          <t>Zed 1.0</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Simon Willison · Tech &amp; Engineering</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://simonwillison.net/2026/Apr/29/llm-3/#atom-everything</t>
+          <t>https://zed.dev/blog/zed-1-0</t>
         </is>
       </c>
     </row>
@@ -6231,44 +6231,44 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>View Rama's recent LinkedIn activity</t>
+          <t>Copy Fail</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+          <t>https://copy.fail/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ghostty is leaving GitHub</t>
+          <t>HERMES.md in commit messages causes requests to route to extra usage billing</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6288,24 +6288,24 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://mitchellh.com/writing/ghostty-leaving-github</t>
+          <t>https://github.com/anthropics/claude-code/issues/53262</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Before GitHub</t>
+          <t>Cursor Camp</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6325,24 +6325,24 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://lucumr.pocoo.org/2026/4/28/before-github/</t>
+          <t>https://neal.fun/cursor-camp/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Bugs Rust won't catch</t>
+          <t>Where the goblins came from</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6362,24 +6362,24 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://corrode.dev/blog/bugs-rust-wont-catch/</t>
+          <t>https://openai.com/index/where-the-goblins-came-from/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Blaster Beam (Musical Instrument)</t>
+          <t>Online age verification is the hill to die on</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6399,24 +6399,24 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Blaster_beam</t>
+          <t>https://x.com/GlennMeder/status/2049088498163216560</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Infisical (YC W23) Is Hiring Full Stack Software Engineers (Remote)</t>
+          <t>We need a federation of forges</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6436,39 +6436,39 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/infisical/782b9da8-20e1-48b2-919e-6c5430c58628</t>
+          <t>https://blog.tangled.org/federation/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Hegseth Cites Falsehood to Defend His Firing of Senior Officers</t>
+          <t>The Zig project's rationale for their anti-AI contribution policy</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>U.S. News</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6478,34 +6478,34 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/us/politics/pete-hegseth-falsehood-firings.html</t>
+          <t>https://simonwillison.net/2026/Apr/30/zig-anti-ai/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mississippi Middle School Students Avert Bus Crash After Driver Loses Control</t>
+          <t>Soft launch of open-source code platform for government</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>U.S. News</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6515,34 +6515,34 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/us/mississippi-students-bus-accident.html</t>
+          <t>https://www.nldigitalgovernment.nl/news/soft-launch-for-government-open-source-code-platform/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Brown University Gunman Planned Attack for Years, F.B.I. Says</t>
+          <t>Mistral Medium 3.5</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>U.S. News</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6552,108 +6552,108 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/us/brown-university-shooting-fbi.html</t>
+          <t>https://mistral.ai/news/vibe-remote-agents-mistral-medium-3-5</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Palestinians Stream Back to Northern Gaza on Foot</t>
+          <t>HashiCorp co-founder says GitHub 'no longer a place for serious work'</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>WSJ · U.S.</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>U.S. News</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/articles/palestinians-flock-back-to-northern-gaza-on-foot-after-hostage-release-breakthrough-3f60e2db</t>
+          <t>https://www.theregister.com/2026/04/29/mitchell_hashimoto_ghostty_quitting_github/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Leading China Property Developer Reports Huge loss, in Sign of Widening Real-Estate Woes</t>
+          <t>FastCGI: 30 years old and still the better protocol for reverse proxies</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>WSJ · U.S.</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>U.S. News</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/articles/even-chinas-property-stalwart-isnt-immune-from-the-crisis-19799863</t>
+          <t>https://www.agwa.name/blog/post/fastcgi_is_the_better_protocol_for_reverse_proxies</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jury Delivers Mixed Verdict in Case of Afghan Charged in 2021 Kabul Attack</t>
+          <t>Kyoto cherry blossoms now bloom earlier than at any point in 1,200 years</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>U.S. News</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6663,34 +6663,34 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/us/politics/mixed-verdict-abbey-gate.html</t>
+          <t>https://jivx.com/kyoto-bloom</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Congress Races to Renew Surveillance Law After House Approval</t>
+          <t>OpenTrafficMap</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>U.S. News</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6700,34 +6700,34 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/us/politics/congress-house-fisa-surveillance-law.html</t>
+          <t>https://opentrafficmap.org/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Civil rights leaders see the voting rights ruling as a ‘betrayal.’</t>
+          <t>Laws of UX</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>U.S. News</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6737,34 +6737,34 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/live/2026/04/29/us/supreme-court-voting-rights/civil-rights-leaders-see-the-voting-rights-ruling-as-a-betrayal</t>
+          <t>https://lawsofux.com/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>‘A Lot of Rocket’: Trump Celebrates Artemis II Astronauts at the White House</t>
+          <t>Maryland becomes first state to ban surveillance pricing in grocery stores</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>U.S. News</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6774,29 +6774,29 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/us/politics/trump-nasa-artemis-astronauts.html</t>
+          <t>https://www.theguardian.com/technology/2026/apr/29/maryland-grocery-stores-ban-surveillance-pricing</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Supreme Court Shakes Up U.S. Political Maps With Voting Rights Act Decision</t>
+          <t>A.I. Spending Sets a Record, With No End in Sight</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>U.S. News</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6811,34 +6811,34 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/us/politics/redistricting-maps-supreme-court-voting.html</t>
+          <t>https://www.nytimes.com/2026/04/29/technology/ai-spending-tech-data-centers.html</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Why Texas Is Winning the Housing War</t>
+          <t>Meta Deal Reversal Deepens Split Between China and Silicon Valley</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6848,34 +6848,34 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/opinion/100000010852250/why-texas-is-winning-the-housing-war.html</t>
+          <t>https://www.nytimes.com/2026/04/29/business/china-silicon-valley-manus.html</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Two Cocky Authoritarians Blocking Hormuz: What Could Go Wrong?</t>
+          <t>United Airlines CEO, Rebuffed by American, Says He’s Skeptical of Other Deals</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6885,66 +6885,66 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/opinion/iran-war-hormuz-blockade.html</t>
+          <t>https://www.nytimes.com/2026/04/29/business/united-airlines-american-scott-kirby.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Building a World ‘Quite Unlike Our Own’</t>
+          <t>Musk Says He ‘Was a Fool’ to Provide OpenAI’s Early Funding</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/opinion/100000010852248/building-a-world-quite-unlike-our-own.html</t>
+          <t>https://www.nytimes.com/2026/04/29/technology/musk-openai-trial-altman.html</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>The Many Ways the Iran War Is Changing the World</t>
+          <t>There’s a 900-Year-Old Answer to Our Most Modern Problem</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6954,34 +6954,34 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/opinion/iran-war-polycrisis.html</t>
+          <t>https://www.nytimes.com/2026/04/30/opinion/ai-crimes-law.html</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Comey and Kimmel: Seashells and a Joke</t>
+          <t>Why Are We Still Driving?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6991,589 +6991,589 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/opinion/james-comey-jimmy-kimmel.html</t>
+          <t>https://www.nytimes.com/2026/04/30/opinion/waymo-self-driving-cars-andrew-miller.html</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>The Loneliness of Donald Trump</t>
+          <t>Fed Meeting Underscores Tough Task Ahead for Warsh</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Economy</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/04/29/opinion/trump-assassination-attempts-political-violence.html</t>
+          <t>https://www.nytimes.com/2026/04/29/business/economy/what-to-watch-at-the-federal-reserves-april-meeting.html</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>IDE Launches Podcast: The Digital Insider with Sinan Aral Podcast | May 30, 2022</t>
+          <t>How Powell Just Complicated Trump’s Fed Plans</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MIT IDE</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://ide.mit.edu/insights/ide-launches-podcast-the-digital-insider-with-sinan-aral/</t>
+          <t>https://www.nytimes.com/2026/04/30/business/dealbook/powell-fed-trump-warsh.html</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>AI and Productivity: Setting Expectations for ROI Blog | April 22, 2026</t>
+          <t>Spirit Airlines Should Die. Why Is Trump Trying to Save It?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MIT IDE</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://ide.mit.edu/insights/ai-productivity-and-roi/</t>
+          <t>https://www.nytimes.com/2026/04/29/opinion/spirit-airlines-trump-bailout-auto.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>The FTC, Consumer Data Collection, and the Future of Online Advertising Blog | April 15, 2026</t>
+          <t>Rising Fuel Prices Force Policymakers to Weigh Excruciating Choices</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MIT IDE</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://ide.mit.edu/insights/the-ftc-consumer-data-collection-and-the-future-of-online-advertising/</t>
+          <t>https://www.nytimes.com/2026/04/30/business/bank-of-england-european-central-bank.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>AI Leaders Dive Into the Business Implications of AI at MIT Blog | April 09, 2026</t>
+          <t>How the Fed’s rate decision affects your finances.</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>MIT IDE</t>
+          <t>NYT · Economy</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://ide.mit.edu/insights/ai-leaders-2026-mit-business-implications-of-ai/</t>
+          <t>https://www.nytimes.com/live/2026/04/29/business/federal-reserve-interest-rates/how-the-feds-rate-decision-affects-your-finances</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>A.I. Is Eliminating Jobs on Wall Street</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>What makes new work different from more work?</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>MIT Shaping Work</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://shapingwork.mit.edu/research/what-makes-new-work-different-from-more-work/</t>
+          <t>https://www.nytimes.com/2026/04/21/business/ai-job-cuts-wall-street.html</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Technology and Economic Development</t>
+          <t>How Good Is Google’s Gemini AI at Making Travel Plans?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>MIT Shaping Work</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://shapingwork.mit.edu/research/technology-and-economic-development/</t>
+          <t>https://www.nytimes.com/2026/04/30/travel/ai-travel-plan-gemini-vacation.html</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Research Insight: What makes new work different from more work?</t>
+          <t>Inside the Courtroom at the OpenAI Trial</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>MIT Shaping Work</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://shapingwork.mit.edu/research/research-insight-what-makes-new-work-different-from-more-work/</t>
+          <t>https://www.nytimes.com/2026/04/30/insider/times-inside-openai-musk-trial.html</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building pro-worker AI</t>
+          <t>Trump Administration Sues New Jersey Governor Over ICE Mask Ban</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>MIT Shaping Work</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://shapingwork.mit.edu/research/building-pro-worker-ai/</t>
+          <t>https://www.nytimes.com/2026/04/29/nyregion/new-jersey-trump-ice-mask-lawsuit.html</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>View Rama's recent LinkedIn activity</t>
+          <t>Silicon Valley Is Bracing for a Permanent Underclass</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+          <t>https://www.nytimes.com/2026/04/30/opinion/ai-labor-work-force-silicon-valley.html</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>‘Scattered Spider’ Member ‘Tylerb’ Pleads Guilty</t>
+          <t>How A.I. Killed Student Writing (and Revived It)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Krebs on Security</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://krebsonsecurity.com/2026/04/scattered-spider-member-tylerb-pleads-guilty/</t>
+          <t>https://www.nytimes.com/2026/04/30/us/ai-students-cheating-homework-classrooms.html</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Patch Tuesday, April 2026 Edition</t>
+          <t>Ford Reports Higher Profit Thanks Partly to Tariff Refund</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Krebs on Security</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://krebsonsecurity.com/2026/04/patch-tuesday-april-2026-edition/</t>
+          <t>https://www.nytimes.com/2026/04/29/business/ford-motor-tariff-refund-profit.html</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Weekly Update 501</t>
+          <t>After Supreme Court Decision, Louisiana Weighs Redrawing House Maps</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Troy Hunt</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.troyhunt.com/weekly-update-501/</t>
+          <t>https://www.nytimes.com/2026/04/30/us/politics/louisiana-suspend-primaries-supreme-court.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Quoting OpenAI Codex base_instructions</t>
+          <t>Forest Service Research Labs Are Closing</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Simon Willison</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://simonwillison.net/2026/Apr/28/openai-codex/#atom-everything</t>
+          <t>https://www.nytimes.com/2026/04/30/climate/forest-service-labs-wildfire-research.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Quoting Matthew Yglesias</t>
+          <t>Leaders at All Levels: How Argenx Scaled to $4 Billion Without Bureaucracy</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Simon Willison</t>
+          <t>MIT Sloan Review · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://simonwillison.net/2026/Apr/28/matthew-yglesias/#atom-everything</t>
+          <t>https://sloanreview.mit.edu/video/leaders-at-all-levels-how-argenx-scaled-to-4-billion-without-bureaucracy/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Steve Ballmer was an underrated CEO</t>
+          <t>OpenAI Trial Starts With Two Very Different Tales of a Company’s Early Years</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Dan Luu</t>
+          <t>Daring Fireball · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7583,34 +7583,34 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://danluu.com/ballmer/</t>
+          <t>https://www.nytimes.com/2026/04/28/technology/openai-trial-elon-musk-sam-altman.html?unlocked_article_code=1.elA.u75G.-STmUe_pILOO</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>How good can you be at Codenames without knowing any words?</t>
+          <t>Playing With Fire</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Dan Luu</t>
+          <t>Daring Fireball · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -7620,29 +7620,29 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://danluu.com/codenames/</t>
+          <t>https://x.com/lifeof_jer/status/2048103471019434248?s=12</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Claude is an Electron App because we’ve lost native</t>
+          <t>LLM 0.32a0 is a major backwards-compatible refactor</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tonsky.me</t>
+          <t>Simon Willison · Tech &amp; Engineering</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -7652,39 +7652,39 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://tonsky.me/blog/fall-of-native/</t>
+          <t>https://simonwillison.net/2026/Apr/29/llm/#atom-everything</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Podcast: На Маке нет никаких шкафов @ Думаем дальше</t>
+          <t>Let's Get Digging!</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tonsky.me</t>
+          <t>Shkspr.mobi · Strategy &amp; Craft</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -7694,29 +7694,29 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://tonsky.me/talks/#2026-01-15</t>
+          <t>https://shkspr.mobi/blog/2026/04/lets-get-digging/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>You can beat the binary search</t>
+          <t>llm 0.32a1</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Lemire.me</t>
+          <t>Simon Willison · Tech &amp; Engineering</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -7726,54 +7726,54 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://lemire.me/blog/2026/04/27/you-can-beat-the-binary-search/</t>
+          <t>https://simonwillison.net/2026/Apr/29/llm-3/#atom-everything</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>The fastest way to match characters on ARM processors?</t>
+          <t>View Rama's recent LinkedIn activity</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Lemire.me</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>social</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t/>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://lemire.me/blog/2026/04/19/the-fastest-way-to-match-characters-on-arm-processors/</t>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>May 2021 Gwern.net Newsletter</t>
+          <t>Ghostty is leaving GitHub</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Gwern.net</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -7800,17 +7800,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://gwern.substack.com/p/may-2021-gwernnet-newsletter</t>
+          <t>https://mitchellh.com/writing/ghostty-leaving-github</t>
         </is>
       </c>
     </row>
@@ -7822,12 +7822,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>April 2021 newsletter</t>
+          <t>Before GitHub</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Gwern.net</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -7837,17 +7837,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://gwern.substack.com/p/april-2021-newsletter</t>
+          <t>https://lucumr.pocoo.org/2026/4/28/before-github/</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>How to Do Great Work</t>
+          <t>Bugs Rust won't catch</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Paul Graham</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -7874,17 +7874,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>http://paulgraham.com/greatwork.html</t>
+          <t>https://corrode.dev/blog/bugs-rust-wont-catch/</t>
         </is>
       </c>
     </row>
@@ -7896,22 +7896,22 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>What Global Turmoil Means for Company Structure</t>
+          <t>Blaster Beam (Musical Instrument)</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>MIT Sloan Review</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://sloanreview.mit.edu/article/what-global-turmoil-means-for-company-structure/</t>
+          <t>https://en.wikipedia.org/wiki/Blaster_beam</t>
         </is>
       </c>
     </row>
@@ -7933,32 +7933,32 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Let's Get Digging!</t>
+          <t>Infisical (YC W23) Is Hiring Full Stack Software Engineers (Remote)</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Shkspr.mobi</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://shkspr.mobi/blog/2026/04/lets-get-digging/</t>
+          <t>https://jobs.ashbyhq.com/infisical/782b9da8-20e1-48b2-919e-6c5430c58628</t>
         </is>
       </c>
     </row>
@@ -7970,32 +7970,32 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Theatre Review: Hadestown ★★★★★</t>
+          <t>Hegseth Cites Falsehood to Defend His Firing of Senior Officers</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Shkspr.mobi</t>
+          <t>NYT · U.S.</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>U.S. News</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>long-form</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://shkspr.mobi/blog/2026/04/theatre-review-hadestown/</t>
+          <t>https://www.nytimes.com/2026/04/29/us/politics/pete-hegseth-falsehood-firings.html</t>
         </is>
       </c>
     </row>
@@ -8007,36 +8007,1553 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
+          <t>Mississippi Middle School Students Avert Bus Crash After Driver Loses Control</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>U.S. News</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/29/us/mississippi-students-bus-accident.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Brown University Gunman Planned Attack for Years, F.B.I. Says</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>U.S. News</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/29/us/brown-university-shooting-fbi.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Palestinians Stream Back to Northern Gaza on Foot</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>WSJ · U.S.</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>U.S. News</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.wsj.com/articles/palestinians-flock-back-to-northern-gaza-on-foot-after-hostage-release-breakthrough-3f60e2db</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Leading China Property Developer Reports Huge loss, in Sign of Widening Real-Estate Woes</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>WSJ · U.S.</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>U.S. News</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.wsj.com/articles/even-chinas-property-stalwart-isnt-immune-from-the-crisis-19799863</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Jury Delivers Mixed Verdict in Case of Afghan Charged in 2021 Kabul Attack</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>U.S. News</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/29/us/politics/mixed-verdict-abbey-gate.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Congress Races to Renew Surveillance Law After House Approval</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>U.S. News</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/29/us/politics/congress-house-fisa-surveillance-law.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Civil rights leaders see the voting rights ruling as a ‘betrayal.’</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>U.S. News</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/live/2026/04/29/us/supreme-court-voting-rights/civil-rights-leaders-see-the-voting-rights-ruling-as-a-betrayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>‘A Lot of Rocket’: Trump Celebrates Artemis II Astronauts at the White House</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>U.S. News</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/29/us/politics/trump-nasa-artemis-astronauts.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Supreme Court Shakes Up U.S. Political Maps With Voting Rights Act Decision</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>U.S. News</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/29/us/politics/redistricting-maps-supreme-court-voting.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Why Texas Is Winning the Housing War</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>NYT · Opinion</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Opinion</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/video/opinion/100000010852250/why-texas-is-winning-the-housing-war.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Two Cocky Authoritarians Blocking Hormuz: What Could Go Wrong?</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>NYT · Opinion</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Opinion</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/29/opinion/iran-war-hormuz-blockade.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Building a World ‘Quite Unlike Our Own’</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>NYT · Opinion</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Opinion</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/video/opinion/100000010852248/building-a-world-quite-unlike-our-own.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>The Many Ways the Iran War Is Changing the World</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>NYT · Opinion</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Opinion</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/29/opinion/iran-war-polycrisis.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Comey and Kimmel: Seashells and a Joke</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>NYT · Opinion</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Opinion</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/29/opinion/james-comey-jimmy-kimmel.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>The Loneliness of Donald Trump</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>NYT · Opinion</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Opinion</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/29/opinion/trump-assassination-attempts-political-violence.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>IDE Launches Podcast: The Digital Insider with Sinan Aral Podcast | May 30, 2022</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>MIT IDE</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://ide.mit.edu/insights/ide-launches-podcast-the-digital-insider-with-sinan-aral/</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>AI and Productivity: Setting Expectations for ROI Blog | April 22, 2026</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>MIT IDE</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://ide.mit.edu/insights/ai-productivity-and-roi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>The FTC, Consumer Data Collection, and the Future of Online Advertising Blog | April 15, 2026</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>MIT IDE</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://ide.mit.edu/insights/the-ftc-consumer-data-collection-and-the-future-of-online-advertising/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>AI Leaders Dive Into the Business Implications of AI at MIT Blog | April 09, 2026</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>MIT IDE</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://ide.mit.edu/insights/ai-leaders-2026-mit-business-implications-of-ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>What makes new work different from more work?</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>MIT Shaping Work</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://shapingwork.mit.edu/research/what-makes-new-work-different-from-more-work/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Technology and Economic Development</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>MIT Shaping Work</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://shapingwork.mit.edu/research/technology-and-economic-development/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Research Insight: What makes new work different from more work?</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>MIT Shaping Work</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://shapingwork.mit.edu/research/research-insight-what-makes-new-work-different-from-more-work/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Building pro-worker AI</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>MIT Shaping Work</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://shapingwork.mit.edu/research/building-pro-worker-ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>View Rama's recent LinkedIn activity</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>‘Scattered Spider’ Member ‘Tylerb’ Pleads Guilty</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Krebs on Security</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://krebsonsecurity.com/2026/04/scattered-spider-member-tylerb-pleads-guilty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Patch Tuesday, April 2026 Edition</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Krebs on Security</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://krebsonsecurity.com/2026/04/patch-tuesday-april-2026-edition/</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Weekly Update 501</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Troy Hunt</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://www.troyhunt.com/weekly-update-501/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Quoting OpenAI Codex base_instructions</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Simon Willison</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://simonwillison.net/2026/Apr/28/openai-codex/#atom-everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Quoting Matthew Yglesias</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Simon Willison</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://simonwillison.net/2026/Apr/28/matthew-yglesias/#atom-everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Steve Ballmer was an underrated CEO</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Dan Luu</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://danluu.com/ballmer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>How good can you be at Codenames without knowing any words?</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Dan Luu</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://danluu.com/codenames/</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Claude is an Electron App because we’ve lost native</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Tonsky.me</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://tonsky.me/blog/fall-of-native/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Podcast: На Маке нет никаких шкафов @ Думаем дальше</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Tonsky.me</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://tonsky.me/talks/#2026-01-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>You can beat the binary search</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Lemire.me</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://lemire.me/blog/2026/04/27/you-can-beat-the-binary-search/</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>The fastest way to match characters on ARM processors?</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Lemire.me</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://lemire.me/blog/2026/04/19/the-fastest-way-to-match-characters-on-arm-processors/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>May 2021 Gwern.net Newsletter</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Gwern.net</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2021-06-11</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://gwern.substack.com/p/may-2021-gwernnet-newsletter</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>April 2021 newsletter</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Gwern.net</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://gwern.substack.com/p/april-2021-newsletter</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>How to Do Great Work</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Paul Graham</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>http://paulgraham.com/greatwork.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>What Global Turmoil Means for Company Structure</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>MIT Sloan Review</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://sloanreview.mit.edu/article/what-global-turmoil-means-for-company-structure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Let's Get Digging!</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Shkspr.mobi</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://shkspr.mobi/blog/2026/04/lets-get-digging/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Theatre Review: Hadestown ★★★★★</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Shkspr.mobi</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://shkspr.mobi/blog/2026/04/theatre-review-hadestown/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
           <t>Rec League</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>Daring Fireball</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="E257" t="inlineStr">
         <is>
           <t>long-form</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
+      <c r="F257" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="G257" t="inlineStr">
         <is>
           <t>https://recleague.com/?lyr_campaign=df</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G216"/>
+  <autoFilter ref="A1:G257"/>
 </worksheet>
 </file>
--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -1051,17 +1051,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>61% of Americans Said They Had to Cut Back on Groceries</t>
+          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NYT · Economy</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/23/us/politics/americans-groceries-inflation-affordability.html</t>
+          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
         </is>
       </c>
     </row>
@@ -1088,17 +1088,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
+          <t>Giving Workers a Stake in A.I. Gains Traction</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
+          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Giving Workers a Stake in A.I. Gains Traction</t>
+          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
         </is>
       </c>
     </row>
@@ -1162,17 +1162,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
+          <t>To A.I. Executives, We’re All Just ‘Meat Computers’</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
+          <t>https://www.nytimes.com/2026/05/24/business/meat-computer-brain-artificial-intelligence.html</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>To A.I. Executives, We’re All Just ‘Meat Computers’</t>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/business/meat-computer-brain-artificial-intelligence.html</t>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
         </is>
       </c>
     </row>
@@ -1236,17 +1236,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+          <t>How Prediction Markets and Crypto Firms Steamrolled a Watchdog Agency</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · U.S.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+          <t>https://www.nytimes.com/2026/05/24/us/how-prediction-markets-and-crypto-firms-steamrolled-a-watchdog-agency.html</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>How Prediction Markets and Crypto Firms Steamrolled a Watchdog Agency</t>
+          <t>61% of Americans Said They Had to Cut Back on Groceries</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>NYT · Economy</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/us/how-prediction-markets-and-crypto-firms-steamrolled-a-watchdog-agency.html</t>
+          <t>https://www.nytimes.com/2026/05/23/us/politics/americans-groceries-inflation-affordability.html</t>
         </is>
       </c>
     </row>

--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -39449,7 +39449,1376 @@
         </is>
       </c>
     </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>The West forgot how to make things, now it’s forgetting how to code</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>https://techtrenches.dev/p/the-west-forgot-how-to-make-things</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>I bought Friendster for $30k – Here's what I'm doing with it</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>https://ca98am79.medium.com/i-bought-friendster-for-30k-heres-what-i-m-doing-with-it-d5e8ddb3991d</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>AI should elevate your thinking, not replace it</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>https://www.koshyjohn.com/blog/ai-should-elevate-your-thinking-not-replace-it/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>An AI agent deleted our production database. The agent's confession is below</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>https://twitter.com/lifeof_jer/status/2048103471019434248</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>GoDaddy gave a domain to a stranger without any documentation</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>https://anchor.host/godaddy-gave-a-domain-to-a-stranger-without-any-documentation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Asahi Linux Progress Linux 7.0</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>https://asahilinux.org/2026/04/progress-report-7-0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Sawe becomes first athlete to run a sub-two-hour marathon in a competitive race</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/athletics/articles/crm1m7e0zwzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Self-updating screenshots</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>https://interblah.net/self-updating-screenshots</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Fast16: High-precision software sabotage 5 years before Stuxnet</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>https://www.sentinelone.com/labs/fast16-mystery-shadowbrokers-reference-reveals-high-precision-software-sabotage-5-years-before-stuxnet/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>SWE-bench Verified no longer measures frontier coding capabilities</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/why-we-no-longer-evaluate-swe-bench-verified/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Statecharts: hierarchical state machines</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>https://statecharts.dev/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>TurboQuant: A first-principles walkthrough</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>https://arkaung.github.io/interactive-turboquant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>The Prompt API</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>https://developer.chrome.com/docs/ai/prompt-api</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Butterflies are in decline across North America, a look at the Western Monarch</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>https://www.smithsonianmag.com/science-nature/butterflies-are-in-dramatic-decline-across-north-america-a-close-look-at-the-western-monarch-shows-why-180988582/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Waymo says can't avoid bike lanes because riders want to be dropped off in them</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>https://road.cc/news/driverless-taxis-veering-into-cycle-lanes-normal-practice-says-waymo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Clay PCB Tutorial</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>https://feministhackerspaces.cargo.site/Clay-PCB-Tutorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>UK Institute Is Hunting for Dangers Lurking in AI</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/technology/uk-ai-safety-institute.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Graduating Into A.I. Pessimism</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/video/opinion/100000010918890/graduating-into-ai-pessimism.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>A.I. Is a Job Creator</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/opinion/ai-job-crisis-goldman-sachs.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Move Over, Private Equity. It’s Great to Be a Banker Again.</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/banks-deals-profits.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>As a Doctor, I Can Understand the Allure of ChatGPT</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/opinion/doctor-ai-chatgpt.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>After Elon Musk’s Court Loss Comes the Long Hot A.I. Summer</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/18/technology/elon-musk-openai-trial.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>A.I. Is Eliminating Jobs on Wall Street</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/21/business/ai-job-cuts-wall-street.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Sundar Pichai Understands Why People Are Anxious About A.I.</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/podcasts/sundar-pichai-understands-why-people-are-anxious-about-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Giving Workers a Stake in A.I. Gains Traction</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>As OpenAI Celebrates Court Win Against Musk, Other Challenges Lie Ahead</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/19/technology/openai-musk-legal-challenges.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>CPI Shows Inflation Accelerating to 3.8% Annually in April After Weeks of War in Iran</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>NYT · Economy</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/12/business/economy/cpi-inflation-report-consumer-prices.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>White House Approves $9 Billion for Spy Agencies to Catch Up on A.I.</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/us/politics/spy-agencies-ai-chips-shortage.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Trump Administration Chips Away at Last Traces of Broad Inquiry Into Jan. 6</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>NYT · Politics</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/us/politics/trump-prosecutors-jan-6.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>It’s Not Just U.S. Stocks. A.I. and Oil Are Moving Global Markets, Too.</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>NYT · Your Money</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Your Money</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/15/business/chip-ai-oil-emerging-stock-markets.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>How Prediction Markets and Crypto Firms Steamrolled a Watchdog Agency</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/us/how-prediction-markets-and-crypto-firms-steamrolled-a-watchdog-agency.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>View Rama's recent LinkedIn activity</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1065"/>
+  <autoFilter ref="A1:G1102"/>
 </worksheet>
 </file>
--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -39452,12 +39452,12 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>The West forgot how to make things, now it’s forgetting how to code</t>
+          <t>Microsoft and OpenAI end their exclusive and revenue-sharing deal</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
@@ -39477,24 +39477,24 @@
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1066" t="inlineStr">
         <is>
-          <t>https://techtrenches.dev/p/the-west-forgot-how-to-make-things</t>
+          <t>https://www.bloomberg.com/news/articles/2026-04-27/microsoft-to-stop-sharing-revenue-with-main-ai-partner-openai</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>I bought Friendster for $30k – Here's what I'm doing with it</t>
+          <t>Talkie: a 13B vintage language model from 1930</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -39514,24 +39514,24 @@
       </c>
       <c r="F1067" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1067" t="inlineStr">
         <is>
-          <t>https://ca98am79.medium.com/i-bought-friendster-for-30k-heres-what-i-m-doing-with-it-d5e8ddb3991d</t>
+          <t>https://talkie-lm.com/introducing-talkie</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>AI should elevate your thinking, not replace it</t>
+          <t>GitHub Copilot is moving to usage-based billing</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
@@ -39551,24 +39551,24 @@
       </c>
       <c r="F1068" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1068" t="inlineStr">
         <is>
-          <t>https://www.koshyjohn.com/blog/ai-should-elevate-your-thinking-not-replace-it/</t>
+          <t>https://github.blog/news-insights/company-news/github-copilot-is-moving-to-usage-based-billing/</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>An AI agent deleted our production database. The agent's confession is below</t>
+          <t>Men who stare at walls</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -39588,24 +39588,24 @@
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1069" t="inlineStr">
         <is>
-          <t>https://twitter.com/lifeof_jer/status/2048103471019434248</t>
+          <t>https://www.alexselimov.com/posts/men_who_stare_at_walls/</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>GoDaddy gave a domain to a stranger without any documentation</t>
+          <t>Is my blue your blue? (2024)</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
@@ -39625,24 +39625,24 @@
       </c>
       <c r="F1070" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1070" t="inlineStr">
         <is>
-          <t>https://anchor.host/godaddy-gave-a-domain-to-a-stranger-without-any-documentation/</t>
+          <t>https://ismy.blue/</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>Asahi Linux Progress Linux 7.0</t>
+          <t>4TB of voice samples just stolen from 40k AI contractors at Mercor</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -39662,24 +39662,24 @@
       </c>
       <c r="F1071" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1071" t="inlineStr">
         <is>
-          <t>https://asahilinux.org/2026/04/progress-report-7-0/</t>
+          <t>https://app.oravys.com/blog/mercor-breach-2026</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>Sawe becomes first athlete to run a sub-two-hour marathon in a competitive race</t>
+          <t>Noctua releases official 3D CAD models for its cooling fans</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
@@ -39699,24 +39699,24 @@
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1072" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/athletics/articles/crm1m7e0zwzo</t>
+          <t>https://www.noctua.at/en/3d-cad-models</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>Self-updating screenshots</t>
+          <t>Pgbackrest is no longer being maintained</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
@@ -39736,24 +39736,24 @@
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1073" t="inlineStr">
         <is>
-          <t>https://interblah.net/self-updating-screenshots</t>
+          <t>https://github.com/pgbackrest/pgbackrest</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>Fast16: High-precision software sabotage 5 years before Stuxnet</t>
+          <t>China blocks Meta's acquisition of AI startup Manus</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
@@ -39773,24 +39773,24 @@
       </c>
       <c r="F1074" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1074" t="inlineStr">
         <is>
-          <t>https://www.sentinelone.com/labs/fast16-mystery-shadowbrokers-reference-reveals-high-precision-software-sabotage-5-years-before-stuxnet/</t>
+          <t>https://www.cnbc.com/2026/04/27/meta-manus-china-blocks-acquisition-ai-startup.html</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>SWE-bench Verified no longer measures frontier coding capabilities</t>
+          <t>Show HN: OSS Agent I built topped the TerminalBench on Gemini-3-flash-preview</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -39810,24 +39810,24 @@
       </c>
       <c r="F1075" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1075" t="inlineStr">
         <is>
-          <t>https://openai.com/index/why-we-no-longer-evaluate-swe-bench-verified/</t>
+          <t>https://github.com/dirac-run/dirac</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>Statecharts: hierarchical state machines</t>
+          <t>You can beat the binary search</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
@@ -39847,24 +39847,24 @@
       </c>
       <c r="F1076" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1076" t="inlineStr">
         <is>
-          <t>https://statecharts.dev/</t>
+          <t>https://lemire.me/blog/2026/04/27/you-can-beat-the-binary-search/</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>TurboQuant: A first-principles walkthrough</t>
+          <t>Dutch central bank ditches AWS and chooses Lidl for European Cloud</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
@@ -39884,24 +39884,24 @@
       </c>
       <c r="F1077" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1077" t="inlineStr">
         <is>
-          <t>https://arkaung.github.io/interactive-turboquant/</t>
+          <t>https://www.techzine.eu/news/infrastructure/140634/dutch-central-bank-chooses-lidl-for-european-cloud/</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>The Prompt API</t>
+          <t>Quarkdown – Markdown with Superpowers</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
@@ -39921,24 +39921,24 @@
       </c>
       <c r="F1078" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1078" t="inlineStr">
         <is>
-          <t>https://developer.chrome.com/docs/ai/prompt-api</t>
+          <t>https://quarkdown.com/</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>Butterflies are in decline across North America, a look at the Western Monarch</t>
+          <t>Super ZSNES – GPU Powered SNES Emulator</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
@@ -39958,24 +39958,24 @@
       </c>
       <c r="F1079" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1079" t="inlineStr">
         <is>
-          <t>https://www.smithsonianmag.com/science-nature/butterflies-are-in-dramatic-decline-across-north-america-a-close-look-at-the-western-monarch-shows-why-180988582/</t>
+          <t>https://zsnes.com/</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>Waymo says can't avoid bike lanes because riders want to be dropped off in them</t>
+          <t>GitHub is having issues now</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
@@ -39995,24 +39995,24 @@
       </c>
       <c r="F1080" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1080" t="inlineStr">
         <is>
-          <t>https://road.cc/news/driverless-taxis-veering-into-cycle-lanes-normal-practice-says-waymo</t>
+          <t>https://www.githubstatus.com</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>Clay PCB Tutorial</t>
+          <t>To my students</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
@@ -40032,19 +40032,19 @@
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G1081" t="inlineStr">
         <is>
-          <t>https://feministhackerspaces.cargo.site/Clay-PCB-Tutorial</t>
+          <t>http://ozark.hendrix.edu/~yorgey/forest/00FD/index.xml</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
@@ -40081,7 +40081,7 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -40118,7 +40118,7 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
@@ -40155,7 +40155,7 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
@@ -40192,7 +40192,7 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
@@ -40229,7 +40229,7 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
@@ -40266,7 +40266,7 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
@@ -40303,7 +40303,7 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
@@ -40340,7 +40340,7 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
@@ -40377,7 +40377,7 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
@@ -40414,7 +40414,7 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
@@ -40451,7 +40451,7 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
@@ -40488,7 +40488,7 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
@@ -40525,7 +40525,7 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
@@ -40562,7 +40562,7 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
@@ -40599,7 +40599,7 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
@@ -40636,7 +40636,7 @@
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
@@ -40673,7 +40673,7 @@
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
@@ -40710,7 +40710,7 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
@@ -40747,7 +40747,7 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
@@ -40784,41 +40784,1447 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Theatre Review: Hadestown ★★★★★</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Shkspr.mobi · Strategy &amp; Craft</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>https://shkspr.mobi/blog/2026/04/theatre-review-hadestown/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>View Rama's recent LinkedIn activity</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="B1102" t="inlineStr">
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>The West forgot how to make things, now it’s forgetting how to code</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>https://techtrenches.dev/p/the-west-forgot-how-to-make-things</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>I bought Friendster for $30k – Here's what I'm doing with it</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>https://ca98am79.medium.com/i-bought-friendster-for-30k-heres-what-i-m-doing-with-it-d5e8ddb3991d</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>AI should elevate your thinking, not replace it</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>https://www.koshyjohn.com/blog/ai-should-elevate-your-thinking-not-replace-it/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>An AI agent deleted our production database. The agent's confession is below</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>https://twitter.com/lifeof_jer/status/2048103471019434248</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>GoDaddy gave a domain to a stranger without any documentation</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>https://anchor.host/godaddy-gave-a-domain-to-a-stranger-without-any-documentation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Asahi Linux Progress Linux 7.0</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>https://asahilinux.org/2026/04/progress-report-7-0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Sawe becomes first athlete to run a sub-two-hour marathon in a competitive race</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/athletics/articles/crm1m7e0zwzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Self-updating screenshots</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>https://interblah.net/self-updating-screenshots</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Fast16: High-precision software sabotage 5 years before Stuxnet</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>https://www.sentinelone.com/labs/fast16-mystery-shadowbrokers-reference-reveals-high-precision-software-sabotage-5-years-before-stuxnet/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>SWE-bench Verified no longer measures frontier coding capabilities</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/why-we-no-longer-evaluate-swe-bench-verified/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Statecharts: hierarchical state machines</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>https://statecharts.dev/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>TurboQuant: A first-principles walkthrough</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>https://arkaung.github.io/interactive-turboquant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>The Prompt API</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>https://developer.chrome.com/docs/ai/prompt-api</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Butterflies are in decline across North America, a look at the Western Monarch</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>https://www.smithsonianmag.com/science-nature/butterflies-are-in-dramatic-decline-across-north-america-a-close-look-at-the-western-monarch-shows-why-180988582/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Waymo says can't avoid bike lanes because riders want to be dropped off in them</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>https://road.cc/news/driverless-taxis-veering-into-cycle-lanes-normal-practice-says-waymo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Clay PCB Tutorial</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>https://feministhackerspaces.cargo.site/Clay-PCB-Tutorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>UK Institute Is Hunting for Dangers Lurking in AI</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/technology/uk-ai-safety-institute.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Graduating Into A.I. Pessimism</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/video/opinion/100000010918890/graduating-into-ai-pessimism.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>A.I. Is a Job Creator</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/opinion/ai-job-crisis-goldman-sachs.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Move Over, Private Equity. It’s Great to Be a Banker Again.</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/banks-deals-profits.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>As a Doctor, I Can Understand the Allure of ChatGPT</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/opinion/doctor-ai-chatgpt.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>After Elon Musk’s Court Loss Comes the Long Hot A.I. Summer</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/18/technology/elon-musk-openai-trial.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>A.I. Is Eliminating Jobs on Wall Street</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/21/business/ai-job-cuts-wall-street.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Sundar Pichai Understands Why People Are Anxious About A.I.</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/podcasts/sundar-pichai-understands-why-people-are-anxious-about-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Giving Workers a Stake in A.I. Gains Traction</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>As OpenAI Celebrates Court Win Against Musk, Other Challenges Lie Ahead</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/19/technology/openai-musk-legal-challenges.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>CPI Shows Inflation Accelerating to 3.8% Annually in April After Weeks of War in Iran</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>NYT · Economy</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/12/business/economy/cpi-inflation-report-consumer-prices.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>White House Approves $9 Billion for Spy Agencies to Catch Up on A.I.</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/us/politics/spy-agencies-ai-chips-shortage.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Trump Administration Chips Away at Last Traces of Broad Inquiry Into Jan. 6</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>NYT · Politics</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/us/politics/trump-prosecutors-jan-6.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>It’s Not Just U.S. Stocks. A.I. and Oil Are Moving Global Markets, Too.</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>NYT · Your Money</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Your Money</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/15/business/chip-ai-oil-emerging-stock-markets.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>How Prediction Markets and Crypto Firms Steamrolled a Watchdog Agency</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/us/how-prediction-markets-and-crypto-firms-steamrolled-a-watchdog-agency.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
         <is>
           <t>View Rama's recent LinkedIn activity</t>
         </is>
       </c>
-      <c r="C1102" t="inlineStr">
+      <c r="C1140" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D1102" t="inlineStr">
+      <c r="D1140" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="E1102" t="inlineStr">
+      <c r="E1140" t="inlineStr">
         <is>
           <t>social</t>
         </is>
       </c>
-      <c r="F1102" t="inlineStr">
+      <c r="F1140" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G1102" t="inlineStr">
+      <c r="G1140" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1102"/>
+  <autoFilter ref="A1:G1140"/>
 </worksheet>
 </file>
--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -42224,7 +42224,1413 @@
         </is>
       </c>
     </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Amateur armed with ChatGPT solves an Erdős problem</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>https://www.scientificamerican.com/article/amateur-armed-with-chatgpt-vibe-maths-a-60-year-old-problem/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>New 10 GbE USB adapters are cooler, smaller, cheaper</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>https://www.jeffgeerling.com/blog/2026/new-10-gbe-usb-adapters-cooler-smaller-cheaper/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Tell HN: An app is silently installing itself on my iPhone every day</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>https://news.ycombinator.com/item?id=47906253</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Trump fires NSF's oversight board</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>https://www.science.org/content/article/trump-fires-nsf-s-oversight-board</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>USB Cheat Sheet (2022)</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>https://fabiensanglard.net/usbcheat/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Why has there been so little progress on Alzheimer's disease?</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>https://freakonomics.com/podcast/why-has-there-been-so-little-progress-on-alzheimers-disease/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>ASML became the chokepoint for cutting-edge chips</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>https://worksinprogress.co/issue/the-worlds-most-complex-machine/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Using coding assistance tools to revive projects you never were going to finish</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>https://blog.matthewbrunelle.com/its-ok-to-use-coding-assistance-tools-to-revive-the-projects-you-never-were-going-to-finish/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Three constraints before I build anything</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>https://jordanlord.co.uk/blog/3-constraints/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>EU Age Control: The trojan horse for digital IDs</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>https://juraj.bednar.io/en/blog-en/2026/04/17/eu-age-control-the-trojan-horse-for-digital-ids/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Fully Featured Audio DSP Firmware for the Raspberry Pi Pico</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>https://github.com/WeebLabs/DSPi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>The AI industry is discovering that the public hates it</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>https://newrepublic.com/article/209163/ai-industry-discovering-public-backlash</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>I have officially retired from Emacs</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>https://nullprogram.com/blog/2026/04/26/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Show HN: A Karpathy-style LLM wiki your agents maintain (Markdown and Git)</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>https://github.com/nex-crm/wuphf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Niri 26.04: Scrollable-tiling Wayland compositor</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>https://github.com/niri-wm/niri/releases/tag/v26.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>The quiet resurgence of RF engineering</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>https://atempleton.bearblog.dev/quiet-resurgence-of-rf-engineering/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>UK Institute Is Hunting for Dangers Lurking in AI</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/technology/uk-ai-safety-institute.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Graduating Into A.I. Pessimism</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/video/opinion/100000010918890/graduating-into-ai-pessimism.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>A.I. Is a Job Creator</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/opinion/ai-job-crisis-goldman-sachs.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Move Over, Private Equity. It’s Great to Be a Banker Again.</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/banks-deals-profits.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>As a Doctor, I Can Understand the Allure of ChatGPT</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/opinion/doctor-ai-chatgpt.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>After Elon Musk’s Court Loss Comes the Long Hot A.I. Summer</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/18/technology/elon-musk-openai-trial.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>A.I. Is Eliminating Jobs on Wall Street</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/21/business/ai-job-cuts-wall-street.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Sundar Pichai Understands Why People Are Anxious About A.I.</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/podcasts/sundar-pichai-understands-why-people-are-anxious-about-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Giving Workers a Stake in A.I. Gains Traction</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>As OpenAI Celebrates Court Win Against Musk, Other Challenges Lie Ahead</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/19/technology/openai-musk-legal-challenges.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>CPI Shows Inflation Accelerating to 3.8% Annually in April After Weeks of War in Iran</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>NYT · Economy</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/12/business/economy/cpi-inflation-report-consumer-prices.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>White House Approves $9 Billion for Spy Agencies to Catch Up on A.I.</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/us/politics/spy-agencies-ai-chips-shortage.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Trump Administration Chips Away at Last Traces of Broad Inquiry Into Jan. 6</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>NYT · Politics</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/us/politics/trump-prosecutors-jan-6.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>It’s Not Just U.S. Stocks. A.I. and Oil Are Moving Global Markets, Too.</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>NYT · Your Money</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Your Money</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/15/business/chip-ai-oil-emerging-stock-markets.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>How Prediction Markets and Crypto Firms Steamrolled a Watchdog Agency</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/us/how-prediction-markets-and-crypto-firms-steamrolled-a-watchdog-agency.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>You can parse an .env file as an .ini with PHP - but there's a catch</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Shkspr.mobi · Strategy &amp; Craft</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>https://shkspr.mobi/blog/2026/04/you-can-parse-an-env-file-as-an-ini-with-php-but-theres-a-catch/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>View Rama's recent LinkedIn activity</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1140"/>
+  <autoFilter ref="A1:G1178"/>
 </worksheet>
 </file>
--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -43630,7 +43630,1413 @@
         </is>
       </c>
     </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>I cancelled Claude: Token issues, declining quality, and poor support</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>https://nickyreinert.de/en/2026/2026-04-24-claude-critics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Google plans to invest up to $40B in Anthropic</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2026-04-24/google-plans-to-invest-up-to-40-billion-in-anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Sabotaging projects by overthinking, scope creep, and structural diffing</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>https://kevinlynagh.com/newsletter/2026_04_overthinking/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Firefox Has Integrated Brave's Adblock Engine</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>https://itsfoss.com/news/firefox-ships-brave-adblock-engine/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Norway set to become latest country to ban social media for under 16s</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2026-04-24/norway-wants-kids-to-be-kids-with-social-media-ban-for-under-16s</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>How to be anti-social – a guide to incoherent and isolating social experiences</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>https://nate.leaflet.pub/3mk4xkaxobc2p</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Replace IBM Quantum back end with /dev/urandom</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>https://github.com/yuvadm/quantumslop/blob/25ad2e76ae58baa96f6219742459407db9dd17f5/URANDOM_DEMO.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>There Will Be a Scientific Theory of Deep Learning</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.21691</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Spinel: Ruby AOT Native Compiler</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>https://github.com/matz/spinel</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>Ubuntu 26.04</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>https://lwn.net/Articles/1069399/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>My audio interface has SSH enabled by default</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>https://hhh.hn/rodecaster-duo-fw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Plain text has been around for decades and it’s here to stay</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>https://unsung.aresluna.org/plain-text-has-been-around-for-decades-and-its-here-to-stay/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>SDL Now Supports DOS</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>https://github.com/libsdl-org/SDL/pull/15377</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Habitual coffee intake shapes the microbiome, modifies physiology and cognition</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/articles/s41467-026-71264-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>The Classic American Diner</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>https://blogs.loc.gov/picturethis/2026/04/the-classic-american-diner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>OpenAI releases GPT-5.5 and GPT-5.5 Pro in the API</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/changelog</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>UK Institute Is Hunting for Dangers Lurking in AI</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/technology/uk-ai-safety-institute.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Graduating Into A.I. Pessimism</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/video/opinion/100000010918890/graduating-into-ai-pessimism.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>A.I. Is a Job Creator</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/opinion/ai-job-crisis-goldman-sachs.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Move Over, Private Equity. It’s Great to Be a Banker Again.</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/banks-deals-profits.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>As a Doctor, I Can Understand the Allure of ChatGPT</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/opinion/doctor-ai-chatgpt.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>After Elon Musk’s Court Loss Comes the Long Hot A.I. Summer</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/18/technology/elon-musk-openai-trial.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>A.I. Is Eliminating Jobs on Wall Street</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/21/business/ai-job-cuts-wall-street.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Sundar Pichai Understands Why People Are Anxious About A.I.</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/podcasts/sundar-pichai-understands-why-people-are-anxious-about-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Giving Workers a Stake in A.I. Gains Traction</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>As OpenAI Celebrates Court Win Against Musk, Other Challenges Lie Ahead</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/19/technology/openai-musk-legal-challenges.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>CPI Shows Inflation Accelerating to 3.8% Annually in April After Weeks of War in Iran</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>NYT · Economy</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/12/business/economy/cpi-inflation-report-consumer-prices.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>White House Approves $9 Billion for Spy Agencies to Catch Up on A.I.</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/us/politics/spy-agencies-ai-chips-shortage.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Trump Administration Chips Away at Last Traces of Broad Inquiry Into Jan. 6</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>NYT · Politics</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/us/politics/trump-prosecutors-jan-6.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>It’s Not Just U.S. Stocks. A.I. and Oil Are Moving Global Markets, Too.</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>NYT · Your Money</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>Your Money</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/15/business/chip-ai-oil-emerging-stock-markets.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>How Prediction Markets and Crypto Firms Steamrolled a Watchdog Agency</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/us/how-prediction-markets-and-crypto-firms-steamrolled-a-watchdog-agency.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Does Mythos mean you need to shut down your Open Source repositories?</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Shkspr.mobi · Strategy &amp; Craft</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>https://shkspr.mobi/blog/2026/04/does-mythos-mean-you-need-to-shut-down-your-open-source-repos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>View Rama's recent LinkedIn activity</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1178"/>
+  <autoFilter ref="A1:G1216"/>
 </worksheet>
 </file>
--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -45036,7 +45036,1450 @@
         </is>
       </c>
     </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>DeepSeek v4</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>https://api-docs.deepseek.com/news/news260424</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/introducing-gpt-5-5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>I am building a cloud</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>https://crawshaw.io/blog/building-a-cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Palantir employees are starting to wonder if they're the bad guys</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/palantir-employees-are-starting-to-wonder-if-theyre-the-bad-guys/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>An update on recent Claude Code quality reports</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/engineering/april-23-postmortem</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Bitwarden CLI compromised in ongoing Checkmarx supply chain campaign</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>https://socket.dev/blog/bitwarden-cli-compromised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Meta tells staff it will cut 10% of jobs</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2026-04-23/meta-tells-staff-it-will-cut-10-of-jobs-in-push-for-efficiency</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>US special forces soldier arrested after allegedly winning $400k on Maduro raid</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>https://www.cnn.com/2026/04/23/politics/us-special-forces-soldier-arrested-maduro-raid-trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Flipdiscs</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>https://flipdisc.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>If America's so rich, how'd it get so sad?</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>https://www.derekthompson.org/p/if-americas-so-rich-howd-it-get-so</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Investigation uncovers two sophisticated telecom surveillance campaigns</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/23/surveillance-vendors-caught-abusing-access-to-telcos-to-track-peoples-phone-locations-researchers-say/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>French government agency confirms breach as hacker offers to sell data</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>https://www.bleepingcomputer.com/news/security/french-govt-agency-confirms-breach-as-hacker-offers-to-sell-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Show HN: Honker – Postgres NOTIFY/LISTEN Semantics for SQLite</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>https://github.com/russellromney/honker</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>MacBook Neo and how the iPad should be</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>https://craigmod.com/essays/ipad_neo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Show HN: Tolaria – Open-source macOS app to manage Markdown knowledge bases</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>https://github.com/refactoringhq/tolaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Why I Write (1946)</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>https://www.orwellfoundation.com/the-orwell-foundation/orwell/essays-and-other-works/why-i-write/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>UK Institute Is Hunting for Dangers Lurking in AI</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/technology/uk-ai-safety-institute.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Graduating Into A.I. Pessimism</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/video/opinion/100000010918890/graduating-into-ai-pessimism.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>A.I. Is a Job Creator</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/opinion/ai-job-crisis-goldman-sachs.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Move Over, Private Equity. It’s Great to Be a Banker Again.</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/banks-deals-profits.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>As a Doctor, I Can Understand the Allure of ChatGPT</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/opinion/doctor-ai-chatgpt.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>After Elon Musk’s Court Loss Comes the Long Hot A.I. Summer</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/18/technology/elon-musk-openai-trial.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>A.I. Is Eliminating Jobs on Wall Street</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/21/business/ai-job-cuts-wall-street.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Sundar Pichai Understands Why People Are Anxious About A.I.</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/podcasts/sundar-pichai-understands-why-people-are-anxious-about-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Giving Workers a Stake in A.I. Gains Traction</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>As OpenAI Celebrates Court Win Against Musk, Other Challenges Lie Ahead</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/19/technology/openai-musk-legal-challenges.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>CPI Shows Inflation Accelerating to 3.8% Annually in April After Weeks of War in Iran</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>NYT · Economy</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/12/business/economy/cpi-inflation-report-consumer-prices.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>White House Approves $9 Billion for Spy Agencies to Catch Up on A.I.</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/us/politics/spy-agencies-ai-chips-shortage.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Trump Administration Chips Away at Last Traces of Broad Inquiry Into Jan. 6</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>NYT · Politics</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/us/politics/trump-prosecutors-jan-6.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>It’s Not Just U.S. Stocks. A.I. and Oil Are Moving Global Markets, Too.</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>NYT · Your Money</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Your Money</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/15/business/chip-ai-oil-emerging-stock-markets.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>How Prediction Markets and Crypto Firms Steamrolled a Watchdog Agency</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/us/how-prediction-markets-and-crypto-firms-steamrolled-a-watchdog-agency.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>OpenAI Beefs Up ChatGPT’s Image Generation Model</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Superpower Daily · Tech &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>https://www.superpowerdaily.com/p/openai-beefs-up-chatgpt-s-image-generation-model</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Sneaky spam in conversational replies to blog posts</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Shkspr.mobi · Strategy &amp; Craft</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>long-form</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>https://shkspr.mobi/blog/2026/04/sneaky-spam-in-conversational-replies-to-blog-posts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>View Rama's recent LinkedIn activity</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1216"/>
+  <autoFilter ref="A1:G1255"/>
 </worksheet>
 </file>
--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -46479,7 +46479,1450 @@
         </is>
       </c>
     </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Framework Laptop 13 Pro</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>https://frame.work/laptop13pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Laws of Software Engineering</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>https://lawsofsoftwareengineering.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>ChatGPT Images 2.0</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/introducing-chatgpt-images-2-0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>SpaceX says it has agreement to acquire Cursor for $60B</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>https://twitter.com/spacex/status/2046713419978453374</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Meta to start capturing employee mouse movements, keystrokes for AI training</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/sustainability/boards-policy-regulation/meta-start-capturing-employee-mouse-movements-keystrokes-ai-training-data-2026-04-21/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Claude Code to be removed from Anthropic's Pro plan?</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>https://bsky.app/profile/edzitron.com/post/3mjzxwfx3qs2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Your hex editor should color-code bytes</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>https://simonomi.dev/blog/color-code-your-bytes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>The Vercel breach: OAuth attack exposes risk in platform environment variables</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>https://www.trendmicro.com/en_us/research/26/d/vercel-breach-oauth-supply-chain.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Britannica11.org – a structured edition of the 1911 Encyclopædia Britannica</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>https://britannica11.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Tim Cook's Impeccable Timing</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>https://stratechery.com/2026/tim-cooks-impeccable-timing/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Drunk post: Things I've learned as a senior engineer (2021)</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>https://luminousmen.substack.com/p/drunk-post-things-ive-learned-as</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Tell HN: I'm sick of AI everything</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>https://news.ycombinator.com/item?id=47857461</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Show HN: VidStudio, a browser based video editor that doesn't upload your files</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>https://vidstudio.app/video-editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>A Roblox cheat and one AI tool brought down Vercel's platform</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>https://webmatrices.com/post/how-a-roblox-cheat-and-one-ai-tool-brought-down-vercel-s-entire-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Anthropic takes $5B from Amazon and pledges $100B in cloud spending in return</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/20/anthropic-takes-5b-from-amazon-and-pledges-100b-in-cloud-spending-in-return/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Original GrapheneOS responses to WIRED fact checker</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>https://discuss.grapheneos.org/d/34369-original-grapheneos-responses-to-wired-fact-checker</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>UK Institute Is Hunting for Dangers Lurking in AI</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/technology/uk-ai-safety-institute.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Graduating Into A.I. Pessimism</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/video/opinion/100000010918890/graduating-into-ai-pessimism.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>A.I. Is a Job Creator</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/opinion/ai-job-crisis-goldman-sachs.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Move Over, Private Equity. It’s Great to Be a Banker Again.</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/banks-deals-profits.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Musk’s SpaceX Goals Shift Ahead of Its I.P.O.</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/22/technology/elon-musk-spacex-ipo-goals.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>As a Doctor, I Can Understand the Allure of ChatGPT</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/opinion/doctor-ai-chatgpt.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>After Elon Musk’s Court Loss Comes the Long Hot A.I. Summer</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/18/technology/elon-musk-openai-trial.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>A.I. Is Eliminating Jobs on Wall Street</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/04/21/business/ai-job-cuts-wall-street.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Sundar Pichai Understands Why People Are Anxious About A.I.</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/podcasts/sundar-pichai-understands-why-people-are-anxious-about-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Giving Workers a Stake in A.I. Gains Traction</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>CPI Shows Inflation Accelerating to 3.8% Annually in April After Weeks of War in Iran</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>NYT · Economy</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/12/business/economy/cpi-inflation-report-consumer-prices.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>White House Approves $9 Billion for Spy Agencies to Catch Up on A.I.</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>NYT · AI</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/22/us/politics/spy-agencies-ai-chips-shortage.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>It’s Not Just U.S. Stocks. A.I. and Oil Are Moving Global Markets, Too.</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>NYT · Your Money</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Your Money</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/15/business/chip-ai-oil-emerging-stock-markets.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Trump Administration Chips Away at Last Traces of Broad Inquiry Into Jan. 6</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>NYT · Politics</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/23/us/politics/trump-prosecutors-jan-6.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>How Prediction Markets and Crypto Firms Steamrolled a Watchdog Agency</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/05/24/us/how-prediction-markets-and-crypto-firms-steamrolled-a-watchdog-agency.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>‘Scattered Spider’ Member ‘Tylerb’ Pleads Guilty</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Krebs on Security · Security &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>https://krebsonsecurity.com/2026/04/scattered-spider-member-tylerb-pleads-guilty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>OpenAI releases Codex ‘Chronicle’ feature for enhancing context</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Superpower Daily · Tech &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>https://www.superpowerdaily.com/p/openai-releases-codex-chronicle-feature-for-enhancing-context</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>View Rama's recent LinkedIn activity</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1255"/>
+  <autoFilter ref="A1:G1294"/>
 </worksheet>
 </file>
--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -200,7 +200,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BambuStudio has been violating PrusaSlicer AGPL license since their fork</t>
+          <t>Microsoft open-sources “the earliest DOS source code discovered to date”</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -225,7 +225,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://twitter.com/josefprusa/status/2054602354851254330</t>
+          <t>https://arstechnica.com/gadgets/2026/04/microsoft-open-sources-the-earliest-dos-source-code-discovered-to-date/</t>
         </is>
       </c>
     </row>
@@ -237,7 +237,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Microsoft open-sources "the earliest DOS source code discovered to date"</t>
+          <t>Wake up! 16b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -262,7 +262,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/gadgets/2026/04/microsoft-open-sources-the-earliest-dos-source-code-discovered-to-date/</t>
+          <t>https://hellmood.111mb.de/wake_up_16b_writeup.html</t>
         </is>
       </c>
     </row>
@@ -274,7 +274,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wake up! 16b</t>
+          <t>BambuStudio has been violating PrusaSlicer AGPL license since their fork</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -299,7 +299,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://hellmood.111mb.de/wake_up_16b_writeup.html</t>
+          <t>https://twitter.com/josefprusa/status/2054602354851254330</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Experience: We found a baby on the subway – now he's our 26-year-old son</t>
+          <t>Scammers are abusing an internal Microsoft account to send spam links</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/lifeandstyle/2026/may/22/experience-found-baby-subway-now-26-year-old-son</t>
+          <t>https://techcrunch.com/2026/05/21/scammers-are-abusing-an-internal-microsoft-account-to-send-spam/</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Scammers are abusing an internal Microsoft account to send spam links</t>
+          <t>Experience: We found a baby on the subway – now he's our 26-year-old son</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/21/scammers-are-abusing-an-internal-microsoft-account-to-send-spam/</t>
+          <t>https://www.theguardian.com/lifeandstyle/2026/may/22/experience-found-baby-subway-now-26-year-old-son</t>
         </is>
       </c>
     </row>
@@ -903,17 +903,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trump Administration Chips Away at Last Traces of Broad Inquiry Into Jan. 6</t>
+          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/23/us/politics/trump-prosecutors-jan-6.html</t>
+          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
         </is>
       </c>
     </row>
@@ -940,17 +940,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
+          <t>Trump Administration Chips Away at Last Traces of Broad Inquiry Into Jan. 6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
+          <t>https://www.nytimes.com/2026/05/23/us/politics/trump-prosecutors-jan-6.html</t>
         </is>
       </c>
     </row>

--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -163,7 +163,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>On The &lt;dl&gt; (2021)</t>
+          <t>Microsoft open-sources “the earliest DOS source code discovered to date”</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -188,7 +188,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://benmyers.dev/blog/on-the-dl/</t>
+          <t>https://arstechnica.com/gadgets/2026/04/microsoft-open-sources-the-earliest-dos-source-code-discovered-to-date/</t>
         </is>
       </c>
     </row>
@@ -200,7 +200,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Microsoft open-sources “the earliest DOS source code discovered to date”</t>
+          <t>On The &lt;dl&gt; (2021)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -225,7 +225,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/gadgets/2026/04/microsoft-open-sources-the-earliest-dos-source-code-discovered-to-date/</t>
+          <t>https://benmyers.dev/blog/on-the-dl/</t>
         </is>
       </c>
     </row>
@@ -385,7 +385,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Italy moves to Airbus A330 tankers</t>
+          <t>Scammers are abusing an internal Microsoft account to send spam links</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -410,7 +410,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.euronews.com/my-europe/2026/05/21/italy-moves-to-airbus-a330-tankers-in-major-nato-aligned-shift</t>
+          <t>https://techcrunch.com/2026/05/21/scammers-are-abusing-an-internal-microsoft-account-to-send-spam/</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>80386 microcode disassembled</t>
+          <t>Italy moves to Airbus A330 tankers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.reenigne.org/blog/80386-microcode-disassembled/</t>
+          <t>https://www.euronews.com/my-europe/2026/05/21/italy-moves-to-airbus-a330-tankers-in-major-nato-aligned-shift</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Scammers are abusing an internal Microsoft account to send spam links</t>
+          <t>80386 microcode disassembled</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/21/scammers-are-abusing-an-internal-microsoft-account-to-send-spam/</t>
+          <t>https://www.reenigne.org/blog/80386-microcode-disassembled/</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-​-dangerously-skip-reading-code</t>
+          <t>Spanish court declines to fine NordVPN over LaLiga piracy blocking order</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://olano.dev/blog/dangerously-skip/</t>
+          <t>https://torrentfreak.com/spanish-court-declines-to-fine-nordvpn-over-laliga-piracy-blocking-order/</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sundar Pichai Understands Why People Are Anxious About A.I.</t>
+          <t>One Job That Is Growing in the A.I. Era? Cybersecurity Experts.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/22/podcasts/sundar-pichai-understands-why-people-are-anxious-about-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/24/technology/one-job-that-is-growing-in-the-ai-era-cybersecurity-experts.html</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>One Job That Is Growing in the A.I. Era? Cybersecurity Experts.</t>
+          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/technology/one-job-that-is-growing-in-the-ai-era-cybersecurity-experts.html</t>
+          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
+          <t>Giving Workers a Stake in A.I. Gains Traction</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
+          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Giving Workers a Stake in A.I. Gains Traction</t>
+          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
         </is>
       </c>
     </row>
@@ -1125,17 +1125,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
+          <t>To A.I. Executives, We’re All Just ‘Meat Computers’</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
+          <t>https://www.nytimes.com/2026/05/24/business/meat-computer-brain-artificial-intelligence.html</t>
         </is>
       </c>
     </row>
@@ -1162,17 +1162,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>To A.I. Executives, We’re All Just ‘Meat Computers’</t>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/business/meat-computer-brain-artificial-intelligence.html</t>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+          <t>How Prediction Markets and Crypto Firms Steamrolled a Watchdog Agency</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · U.S.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+          <t>https://www.nytimes.com/2026/05/24/us/how-prediction-markets-and-crypto-firms-steamrolled-a-watchdog-agency.html</t>
         </is>
       </c>
     </row>
@@ -1236,17 +1236,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>How Prediction Markets and Crypto Firms Steamrolled a Watchdog Agency</t>
+          <t>61% of Americans Said They Had to Cut Back on Groceries</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>NYT · Economy</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/us/how-prediction-markets-and-crypto-firms-steamrolled-a-watchdog-agency.html</t>
+          <t>https://www.nytimes.com/2026/05/23/us/politics/americans-groceries-inflation-affordability.html</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>61% of Americans Said They Had to Cut Back on Groceries</t>
+          <t>Pope Leo Is Set to Release an Encyclical About A.I. Why Is That Important?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NYT · Economy</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/23/us/politics/americans-groceries-inflation-affordability.html</t>
+          <t>https://www.nytimes.com/2026/05/25/world/europe/pope-leo-encyclical-ai.html</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gov. Gavin Newsom to Sign Executive Order Aimed at A.I. Job Loss</t>
+          <t>Sundar Pichai Understands Why People Are Anxious About A.I.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/technology/newsom-ai-executive-order-california.html</t>
+          <t>https://www.nytimes.com/2026/05/22/podcasts/sundar-pichai-understands-why-people-are-anxious-about-ai.html</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Google Appeals Landmark Ruling Declaring It a Monopolist in Search</t>
+          <t>Gov. Gavin Newsom to Sign Executive Order Aimed at A.I. Job Loss</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/22/technology/google-appeals-search-case.html</t>
+          <t>https://www.nytimes.com/2026/05/21/technology/newsom-ai-executive-order-california.html</t>
         </is>
       </c>
     </row>

--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Time to talk about my writerdeck</t>
+          <t>Microsoft open-sources “the earliest DOS source code discovered to date”</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://veronicaexplains.net/my-first-writerdeck/</t>
+          <t>https://arstechnica.com/gadgets/2026/04/microsoft-open-sources-the-earliest-dos-source-code-discovered-to-date/</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Microsoft open-sources “the earliest DOS source code discovered to date”</t>
+          <t>Time to talk about my writerdeck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/gadgets/2026/04/microsoft-open-sources-the-earliest-dos-source-code-discovered-to-date/</t>
+          <t>https://veronicaexplains.net/my-first-writerdeck/</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Oura says it gets government demands for user data</t>
+          <t>Scammers are abusing an internal Microsoft account to send spam links</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://this.weekinsecurity.com/oura-says-it-gets-government-demands-for-user-data-will-it-share-how-many/</t>
+          <t>https://techcrunch.com/2026/05/21/scammers-are-abusing-an-internal-microsoft-account-to-send-spam/</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Scammers are abusing an internal Microsoft account to send spam links</t>
+          <t>Oura says it gets government demands for user data</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/21/scammers-are-abusing-an-internal-microsoft-account-to-send-spam/</t>
+          <t>https://this.weekinsecurity.com/oura-says-it-gets-government-demands-for-user-data-will-it-share-how-many/</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>US tech firms share Dutch regulator officials' names with Senate</t>
+          <t>Spanish court declines to fine NordVPN over LaLiga piracy blocking order</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.dutchnews.nl/2026/05/us-tech-firms-share-dutch-regulator-officials-names-with-senate/</t>
+          <t>https://torrentfreak.com/spanish-court-declines-to-fine-nordvpn-over-laliga-piracy-blocking-order/</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The FBI Wants 'Near Real-Time' Access to US License Plate Readers</t>
+          <t>US tech firms share Dutch regulator officials' names with Senate</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.wired.com/story/security-news-this-week-fbi-license-plate-reader-real-time-access/</t>
+          <t>https://www.dutchnews.nl/2026/05/us-tech-firms-share-dutch-regulator-officials-names-with-senate/</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Spanish court declines to fine NordVPN over LaLiga piracy blocking order</t>
+          <t>The FBI Wants 'Near Real-Time' Access to US License Plate Readers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://torrentfreak.com/spanish-court-declines-to-fine-nordvpn-over-laliga-piracy-blocking-order/</t>
+          <t>https://www.wired.com/story/security-news-this-week-fbi-license-plate-reader-real-time-access/</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UK Institute Is Hunting for Dangers Lurking in AI</t>
+          <t>Artificial Intelligence Floods Court Dockets with Home-Brewed Lawsuits</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/technology/uk-ai-safety-institute.html</t>
+          <t>https://www.nytimes.com/2026/05/25/us/politics/artificial-intelliegence-courts.html</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
+          <t>UK Institute Is Hunting for Dangers Lurking in AI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2250,17 +2250,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
+          <t>https://www.nytimes.com/2026/05/24/technology/uk-ai-safety-institute.html</t>
         </is>
       </c>
     </row>
@@ -2346,22 +2346,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A.I. Is a Job Creator</t>
+          <t>Move Over, Private Equity. It’s Great to Be a Banker Again.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/22/opinion/ai-job-crisis-goldman-sachs.html</t>
+          <t>https://www.nytimes.com/2026/05/22/business/banks-deals-profits.html</t>
         </is>
       </c>
     </row>
@@ -2383,32 +2383,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Move Over, Private Equity. It’s Great to Be a Banker Again.</t>
+          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · Sunday Opinion</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Sunday Opinion</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/22/business/banks-deals-profits.html</t>
+          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
         </is>
       </c>
     </row>
@@ -2457,17 +2457,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Trump Administration Chips Away at Last Traces of Broad Inquiry Into Jan. 6</t>
+          <t>Pope Leo Warns of A.I. Risks in His First Papal Encyclical</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/23/us/politics/trump-prosecutors-jan-6.html</t>
+          <t>https://www.nytimes.com/video/world/europe/100000010924143/pope-leo-ai-encyclical-risks.html</t>
         </is>
       </c>
     </row>
@@ -2494,17 +2494,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>One Job That Is Growing in the A.I. Era? Cybersecurity Experts.</t>
+          <t>Trump Administration Chips Away at Last Traces of Broad Inquiry Into Jan. 6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/technology/one-job-that-is-growing-in-the-ai-era-cybersecurity-experts.html</t>
+          <t>https://www.nytimes.com/2026/05/23/us/politics/trump-prosecutors-jan-6.html</t>
         </is>
       </c>
     </row>
@@ -2531,17 +2531,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
+          <t>Main Takeaways From Pope Leo’s Encyclical on A.I.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
+          <t>https://www.nytimes.com/2026/05/25/us/pope-leo-encyclical-highlights.html</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Giving Workers a Stake in A.I. Gains Traction</t>
+          <t>One Job That Is Growing in the A.I. Era? Cybersecurity Experts.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/24/technology/ai-cybersecurity-jobs.html</t>
         </is>
       </c>
     </row>
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
+          <t>As A.I. Fever Rises in Silicon Valley, Pope Leo Has a Few Words</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
+          <t>https://www.nytimes.com/2026/05/25/technology/pope-ai-silicon-valley.html</t>
         </is>
       </c>
     </row>
@@ -2642,17 +2642,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>To A.I. Executives, We’re All Just ‘Meat Computers’</t>
+          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2662,12 +2662,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/business/meat-computer-brain-artificial-intelligence.html</t>
+          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
         </is>
       </c>
     </row>
@@ -2679,17 +2679,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+          <t>Giving Workers a Stake in A.I. Gains Traction</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
         </is>
       </c>
     </row>
@@ -2716,17 +2716,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>How Prediction Markets and Crypto Firms Steamrolled a Watchdog Agency</t>
+          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/us/how-prediction-markets-and-crypto-firms-steamrolled-a-watchdog-agency.html</t>
+          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
         </is>
       </c>
     </row>
@@ -2753,17 +2753,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>61% of Americans Said They Had to Cut Back on Groceries</t>
+          <t>To A.I. Executives, We’re All Just ‘Meat Computers’</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NYT · Economy</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2773,12 +2773,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/23/us/politics/americans-groceries-inflation-affordability.html</t>
+          <t>https://www.nytimes.com/2026/05/24/business/meat-computer-brain-artificial-intelligence.html</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pope Leo Is Set to Release an Encyclical About A.I. Why Is That Important?</t>
+          <t>Iran Is Trolling Us and We’re Not Doing Anything About It</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/25/world/europe/pope-leo-encyclical-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/25/opinion/iran-trolling-propaganda.html</t>
         </is>
       </c>
     </row>
@@ -2827,17 +2827,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>White House Approves $9 Billion for Spy Agencies to Catch Up on A.I.</t>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/22/us/politics/spy-agencies-ai-chips-shortage.html</t>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
         </is>
       </c>
     </row>
@@ -2864,17 +2864,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sundar Pichai Understands Why People Are Anxious About A.I.</t>
+          <t>61% of Americans Said They Had to Cut Back on Groceries</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · Economy</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2884,12 +2884,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/22/podcasts/sundar-pichai-understands-why-people-are-anxious-about-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/23/us/politics/americans-groceries-inflation-affordability.html</t>
         </is>
       </c>
     </row>
@@ -2901,17 +2901,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gov. Gavin Newsom to Sign Executive Order Aimed at A.I. Job Loss</t>
+          <t>Pope Leo Warns of Risks From A.I. in 42,300-Word Encyclical</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/technology/newsom-ai-executive-order-california.html</t>
+          <t>https://www.nytimes.com/2026/05/25/world/europe/pope-leo-encyclical.html</t>
         </is>
       </c>
     </row>

--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -163,7 +163,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Migrating from Go to Rust</t>
+          <t>The Eternal Sloptember</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -188,7 +188,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://corrode.dev/learn/migration-guides/go-to-rust/</t>
+          <t>https://geohot.github.io//blog/jekyll/update/2026/05/24/the-eternal-sloptember.html</t>
         </is>
       </c>
     </row>
@@ -200,7 +200,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Eternal Sloptember</t>
+          <t>Migrating from Go to Rust</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -225,7 +225,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://geohot.github.io//blog/jekyll/update/2026/05/24/the-eternal-sloptember.html</t>
+          <t>https://corrode.dev/learn/migration-guides/go-to-rust/</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Usborne 1980s Computer Books</t>
+          <t>Building Pi with Pi</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://usborne.com/us/books/computer-and-coding-books</t>
+          <t>https://lucumr.pocoo.org/2026/5/24/pi-oss/</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Floods Court Dockets with Home-Brewed Lawsuits</t>
+          <t>OpenRouter, an Exchange for A.I. Models, Raises $113 Million</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/25/us/politics/artificial-intelliegence-courts.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/dealbook/openrouter-ai-models-fundraising.html</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UK Institute Is Hunting for Dangers Lurking in AI</t>
+          <t>The Vatican Takes on Silicon Valley With an A.I. Warning</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/technology/uk-ai-safety-institute.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/dealbook/vatican-ai-silicon-valley.html</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>As a Doctor, I Can Understand the Allure of ChatGPT</t>
+          <t>To Understand Pope Leo’s Efforts on A.I., Look at the Man Shaking His Hand</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -770,17 +770,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/opinion/doctor-ai-chatgpt.html</t>
+          <t>https://www.nytimes.com/2026/05/26/us/pope-leo-ai-anthropic.html</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Graduating Into A.I. Pessimism</t>
+          <t>Progressives Are Listening to the Wrong People on A.I.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/opinion/100000010918890/graduating-into-ai-pessimism.html</t>
+          <t>https://www.nytimes.com/2026/05/26/opinion/progressives-left-ai.html</t>
         </is>
       </c>
     </row>
@@ -829,22 +829,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
+          <t>Artificial Intelligence Floods Court Dockets with Home-Brewed Lawsuits</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NYT · Sunday Opinion</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sunday Opinion</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
+          <t>https://www.nytimes.com/2026/05/25/us/politics/artificial-intelliegence-courts.html</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pope Leo Warns of A.I. Risks in His First Papal Encyclical</t>
+          <t>White House Shakes Up Green Card Policy, and the Pope Takes On A.I.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/world/europe/100000010924143/pope-leo-ai-encyclical-risks.html</t>
+          <t>https://www.nytimes.com/2026/05/26/podcasts/the-headlines/white-house-green-card-pope-ai.html</t>
         </is>
       </c>
     </row>
@@ -903,17 +903,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Move Over, Private Equity. It’s Great to Be a Banker Again.</t>
+          <t>UK Institute Is Hunting for Dangers Lurking in AI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/22/business/banks-deals-profits.html</t>
+          <t>https://www.nytimes.com/2026/05/24/technology/uk-ai-safety-institute.html</t>
         </is>
       </c>
     </row>
@@ -940,17 +940,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Main Takeaways From Pope Leo’s Encyclical on A.I.</t>
+          <t>Global Oil Price Rises After U.S. Strikes in Iran Cloud Peace Deal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/25/us/pope-leo-encyclical-highlights.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/oil-gas-price-iran.html</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>One Job That Is Growing in the A.I. Era? Cybersecurity Experts.</t>
+          <t>SpaceX IPO Filing Reveals Favorable Terms for Elon Musk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/technology/ai-cybersecurity-jobs.html</t>
+          <t>https://www.nytimes.com/2026/05/26/technology/spacex-elon-musk-pay-board-governance.html</t>
         </is>
       </c>
     </row>
@@ -1014,22 +1014,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>As A.I. Fever Rises in Silicon Valley, Pope Leo Has a Few Words</t>
+          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Sunday Opinion</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Sunday Opinion</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/25/technology/pope-ai-silicon-valley.html</t>
+          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>To A.I. Executives, We’re All Just ‘Meat Computers’</t>
+          <t>You Can’t Stop This Data Center, a Mom Was Told. She Won’t Quit.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/business/meat-computer-brain-artificial-intelligence.html</t>
+          <t>https://www.nytimes.com/2026/05/26/us/data-centers-kassi-solberg.html</t>
         </is>
       </c>
     </row>
@@ -1088,32 +1088,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Iran Is Trolling Us and We’re Not Doing Anything About It</t>
+          <t>Eli Lilly to Buy 3 Vaccine Developers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/25/opinion/iran-trolling-propaganda.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/eli-lilly-vaccines-shingles-epstein-barr.html</t>
         </is>
       </c>
     </row>
@@ -1125,17 +1125,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+          <t>At the A.I. Epicenter, Technologists Dismiss Pope Leo’s Warnings About the New Technology</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+          <t>https://www.nytimes.com/2026/05/26/technology/pope-leo-ai-religion.html</t>
         </is>
       </c>
     </row>
@@ -1162,17 +1162,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
+          <t>As A.I. Fever Rises in Silicon Valley, Pope Leo Has a Few Words</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
+          <t>https://www.nytimes.com/2026/05/25/technology/pope-ai-silicon-valley.html</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pope Leo Warns of Risks From A.I. in 42,300-Word Encyclical</t>
+          <t>Yuval Noah Harari on Donald Trump’s Core Delusion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1214,17 +1214,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/25/world/europe/pope-leo-encyclical.html</t>
+          <t>https://www.nytimes.com/2026/05/26/opinion/ezra-klein-podcast-yuval-noah-harari.html</t>
         </is>
       </c>
     </row>
@@ -1236,32 +1236,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Trump Cancels Signing of Executive Order Granting Oversight of A.I. Models</t>
+          <t>Pope Leo’s Encyclical on A.I. Is Disappointingly Mild</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/technology/trump-ai-executive-order.html</t>
+          <t>https://www.nytimes.com/2026/05/26/opinion/pope-leo-encyclical-ai.html</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Giving Workers a Stake in A.I. Gains Traction</t>
+          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/22/business/dealbook/newsom-universal-basic-capital-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
         </is>
       </c>
     </row>
@@ -1310,17 +1310,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SpaceX, OpenAI and Anthropic Race to Go Public</t>
+          <t>Should You Take Nutrition Advice From a Chatbot?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/business/dealbook/spacex-openai-anthropic-ipo.html</t>
+          <t>https://www.nytimes.com/2026/05/26/well/eat/ai-chatbots-nutrition-advice.html</t>
         </is>
       </c>
     </row>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A Democrat Took on Red Sox Ownership in an Ad. A Network Pulled it.</t>
+          <t>E.P.A. to Repeal Some Limits on ‘Forever Chemicals’ in Drinking Water</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/us/politics/platner-ad-red-sox-midterms.html</t>
+          <t>https://www.nytimes.com/2026/05/18/climate/epa-forever-chemicals-pfas-drinking-water.html</t>
         </is>
       </c>
     </row>
@@ -1384,17 +1384,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Trump Administration Chips Away at Last Traces of Broad Inquiry Into Jan. 6</t>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/23/us/politics/trump-prosecutors-jan-6.html</t>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
         </is>
       </c>
     </row>

--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -200,7 +200,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Big tech's anti-labor playbook has come for Wikipedia</t>
+          <t>The worst job interview I ever had</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -225,7 +225,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://medium.com/@jakeorlowitz/wikipedia-is-doing-the-capitalist-thing-56a393232943</t>
+          <t>https://www.oliverio.dev/blog/the-worst-job-interview-i-had</t>
         </is>
       </c>
     </row>
@@ -237,7 +237,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The real cost of owning a home</t>
+          <t>Big tech's anti-labor playbook has come for Wikipedia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -262,7 +262,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://ericturner.dev/posts/cost-of-home-ownership/</t>
+          <t>https://medium.com/@jakeorlowitz/wikipedia-is-doing-the-capitalist-thing-56a393232943</t>
         </is>
       </c>
     </row>
@@ -274,7 +274,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dropbox CEO Drew Houston to step down</t>
+          <t>The real cost of owning a home</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -299,7 +299,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/05/26/dropbox-ceo-drew-houston-ashraf-alkarmi.html</t>
+          <t>https://ericturner.dev/posts/cost-of-home-ownership/</t>
         </is>
       </c>
     </row>
@@ -348,7 +348,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DynIP – Dynamic DNS with RFC 2136, IPv6, DNSSEC, and BYOD</t>
+          <t>Dropbox CEO Drew Houston to step down</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -373,7 +373,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://dynip.dev/</t>
+          <t>https://www.cnbc.com/2026/05/26/dropbox-ceo-drew-houston-ashraf-alkarmi.html</t>
         </is>
       </c>
     </row>
@@ -385,7 +385,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The worst job interview I ever had</t>
+          <t>DynIP – Dynamic DNS with RFC 2136, IPv6, DNSSEC, and BYOD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -410,7 +410,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliverio.dev/blog/the-worst-job-interview-i-had</t>
+          <t>https://dynip.dev/</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The user is visibly frustrated</t>
+          <t>Cloudflare Flagship</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pscanf.com/s/354/</t>
+          <t>https://developers.cloudflare.com/flagship/</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Uber president says AI spending is getting 'harder to justify'</t>
+          <t>Stripe is friendly to “friendly fraud”</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/transportation/937116/uber-ai-investment-hard-to-justify</t>
+          <t>https://www.gingerlime.com/2026/stripe-seem-friendly-to-friendly-fraud/</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Uber, Lyft drivers in Massachusetts form first US ride-share union</t>
+          <t>Uber president says AI spending is getting 'harder to justify'</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/world-at-work/uber-lyft-drivers-massachusetts-form-first-us-ride-share-union-2026-05-26/</t>
+          <t>https://www.theverge.com/transportation/937116/uber-ai-investment-hard-to-justify</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stripe is friendly to “friendly fraud”</t>
+          <t>The user is visibly frustrated</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.gingerlime.com/2026/stripe-seem-friendly-to-friendly-fraud/</t>
+          <t>https://pscanf.com/s/354/</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Erin Brockovich made a map to track data centers around the country</t>
+          <t>Uber, Lyft drivers in Massachusetts form first US ride-share union</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.niemanlab.org/2026/05/erin-brockovich-made-a-map-to-track-data-centers-around-the-country/</t>
+          <t>https://www.reuters.com/business/world-at-work/uber-lyft-drivers-massachusetts-form-first-us-ride-share-union-2026-05-26/</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cloudflare Flagship</t>
+          <t>Erin Brockovich made a map to track data centers around the country</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://developers.cloudflare.com/flagship/</t>
+          <t>https://www.niemanlab.org/2026/05/erin-brockovich-made-a-map-to-track-data-centers-around-the-country/</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OpenRouter, an Exchange for A.I. Models, Raises $113 Million</t>
+          <t>Two of America’s Thorniest Political Issues Are Dividing an Arizona Town</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/business/dealbook/openrouter-ai-models-fundraising.html</t>
+          <t>https://www.nytimes.com/2026/05/27/us/politics/marana-arizona-data-center-ice-detention.html</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>When Two Heated Political Issues Descended on One Swing District Town</t>
+          <t>Why Memory Chips Are Dominating the A.I. Rally</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/27/us/politics/marana-arizona-data-center-ice-detention.html</t>
+          <t>https://www.nytimes.com/2026/05/27/business/dealbook/ai-chips-war-samsung-micron.html</t>
         </is>
       </c>
     </row>
@@ -755,17 +755,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Vatican Takes on Silicon Valley With an A.I. Warning</t>
+          <t>OpenRouter, an Exchange for A.I. Models, Raises $113 Million</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/business/dealbook/vatican-ai-silicon-valley.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/dealbook/openrouter-ai-models-fundraising.html</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>White House Shakes Up Green Card Policy, and the Pope Takes On A.I.</t>
+          <t>The Two Issues That Could Swing This District</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/podcasts/the-headlines/white-house-green-card-pope-ai.html</t>
+          <t>https://www.nytimes.com/video/us/100000010903992/ai-data-center-ice-detention-center-arizona.html</t>
         </is>
       </c>
     </row>
@@ -829,17 +829,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Two Issues That Could Swing This District</t>
+          <t>The Vatican Takes on Silicon Valley With an A.I. Warning</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/us/100000010903992/the-two-issues-that-could-swing-this-district.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/dealbook/vatican-ai-silicon-valley.html</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Go Ask Alice Why Tech Start-Ups Are Spending Big on Hype Videos</t>
+          <t>Teachers Union Urges Schools to Curb A.I. Chatbots and Screen Time</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/27/technology/ai-startups-videos-marketing.html</t>
+          <t>https://www.nytimes.com/2026/05/27/technology/ai-screens-schools-weingarten.html</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eli Lilly to Buy 3 Vaccine Developers</t>
+          <t>At the A.I. Epicenter, Technologists Dismiss Pope Leo’s Warnings About the New Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/business/eli-lilly-vaccines-shingles-epstein-barr.html</t>
+          <t>https://www.nytimes.com/2026/05/26/technology/pope-leo-ai-religion.html</t>
         </is>
       </c>
     </row>
@@ -1088,22 +1088,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>At the A.I. Epicenter, Technologists Dismiss Pope Leo’s Warnings About the New Technology</t>
+          <t>Progressives Are Listening to the Wrong People on A.I.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/technology/pope-leo-ai-religion.html</t>
+          <t>https://www.nytimes.com/2026/05/26/opinion/progressives-left-ai.html</t>
         </is>
       </c>
     </row>
@@ -1125,17 +1125,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Progressives Are Listening to the Wrong People on A.I.</t>
+          <t>Writing Is Fundamental to How We Think</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/opinion/progressives-left-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/27/opinion/writing-creativity-ai.html</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Writing Is Fundamental to How We Think</t>
+          <t>E.P.A. to Repeal Some Limits on ‘Forever Chemicals’ in Drinking Water</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/27/opinion/writing-creativity-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/18/climate/epa-forever-chemicals-pfas-drinking-water.html</t>
         </is>
       </c>
     </row>
@@ -1199,22 +1199,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>E.P.A. to Repeal Some Limits on ‘Forever Chemicals’ in Drinking Water</t>
+          <t>As a Doctor, I Can Understand the Allure of ChatGPT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/18/climate/epa-forever-chemicals-pfas-drinking-water.html</t>
+          <t>https://www.nytimes.com/2026/05/24/opinion/doctor-ai-chatgpt.html</t>
         </is>
       </c>
     </row>
@@ -1236,32 +1236,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>As a Doctor, I Can Understand the Allure of ChatGPT</t>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/opinion/doctor-ai-chatgpt.html</t>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+          <t>Mayes Middleton Defeats Chip Roy in the Runoff for Texas Attorney General</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+          <t>https://www.nytimes.com/2026/05/26/us/politics/texas-attorney-general.html</t>
         </is>
       </c>
     </row>
@@ -1310,17 +1310,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Supreme Court Reverses Ruling in Immigration Judges’ Free Speech Lawsuit</t>
+          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/us/politics/supreme-court-immigration-judges.html</t>
+          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
         </is>
       </c>
     </row>
@@ -1347,32 +1347,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
+          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Sunday Opinion</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Sunday Opinion</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
+          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
         </is>
       </c>
     </row>
@@ -1384,32 +1384,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
+          <t>How Cannes Is Grappling With Changes</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NYT · Sunday Opinion</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sunday Opinion</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
+          <t>https://www.nytimes.com/video/movies/100000010860400/alissa-reviews-cannes.html</t>
         </is>
       </c>
     </row>

--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Global Oil Price Rises After U.S. Strikes in Iran Cloud Peace Deal</t>
+          <t>KFF’s Chief Executive to Retire</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/business/oil-gas-price-iran.html</t>
+          <t>https://www.nytimes.com/2026/05/27/business/media/kff-drew-altman.html</t>
         </is>
       </c>
     </row>
@@ -2420,17 +2420,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SpaceX IPO Filing Reveals Favorable Terms for Elon Musk</t>
+          <t>Global Oil Price Rises After U.S. Strikes in Iran Cloud Peace Deal</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/technology/spacex-elon-musk-pay-board-governance.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/oil-gas-price-iran.html</t>
         </is>
       </c>
     </row>
@@ -2457,17 +2457,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Teachers Union Urges Schools to Curb A.I. Chatbots and Screen Time</t>
+          <t>SpaceX IPO Filing Reveals Favorable Terms for Elon Musk</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/27/technology/ai-screens-schools-weingarten.html</t>
+          <t>https://www.nytimes.com/2026/05/26/technology/spacex-elon-musk-pay-board-governance.html</t>
         </is>
       </c>
     </row>
@@ -2531,22 +2531,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>At the A.I. Epicenter, Technologists Dismiss Pope Leo’s Warnings About the New Technology</t>
+          <t>Progressives Are Listening to the Wrong People on A.I.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/technology/pope-leo-ai-religion.html</t>
+          <t>https://www.nytimes.com/2026/05/26/opinion/progressives-left-ai.html</t>
         </is>
       </c>
     </row>
@@ -2568,32 +2568,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Progressives Are Listening to the Wrong People on A.I.</t>
+          <t>As A.I. Fever Rises in Silicon Valley, Pope Leo Has a Few Words</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/opinion/progressives-left-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/25/technology/pope-ai-silicon-valley.html</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>As A.I. Fever Rises in Silicon Valley, Pope Leo Has a Few Words</t>
+          <t>A.I. Money From I.P.O.s Will Change Philanthropy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2620,17 +2620,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/25/technology/pope-ai-silicon-valley.html</t>
+          <t>https://www.nytimes.com/2026/05/27/opinion/ai-philanthropy-charity.html</t>
         </is>
       </c>
     </row>
@@ -2753,32 +2753,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>As a Doctor, I Can Understand the Allure of ChatGPT</t>
+          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/opinion/doctor-ai-chatgpt.html</t>
+          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
         </is>
       </c>
     </row>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Rising Energy Costs and Data Centers at Heart of NextEra’s Dominion Bid</t>
+          <t>Mayes Middleton Defeats Chip Roy in the Runoff for Texas Attorney General</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/19/business/energy-environment/nextera-dominion-electricity-rates-data-centers.html</t>
+          <t>https://www.nytimes.com/2026/05/26/us/politics/texas-attorney-general.html</t>
         </is>
       </c>
     </row>
@@ -2827,17 +2827,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mayes Middleton Defeats Chip Roy in the Runoff for Texas Attorney General</t>
+          <t>At the A.I. Epicenter, Technologists Dismiss Pope Leo’s Warnings About the New Technology</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/us/politics/texas-attorney-general.html</t>
+          <t>https://www.nytimes.com/2026/05/26/technology/pope-leo-ai-religion.html</t>
         </is>
       </c>
     </row>

--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -163,7 +163,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Netherlands blocks US takeover of vital digital supplier</t>
+          <t>The worst job interview I ever had</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -188,7 +188,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.politico.eu/article/netherlands-blocks-us-takeover-vital-digital-supplier/</t>
+          <t>https://www.oliverio.dev/blog/the-worst-job-interview-i-had</t>
         </is>
       </c>
     </row>
@@ -200,7 +200,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The worst job interview I ever had</t>
+          <t>Netherlands blocks US takeover of vital digital supplier</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -225,7 +225,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliverio.dev/blog/the-worst-job-interview-i-had</t>
+          <t>https://www.politico.eu/article/netherlands-blocks-us-takeover-vital-digital-supplier/</t>
         </is>
       </c>
     </row>
@@ -274,7 +274,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The real cost of owning a home</t>
+          <t>That Methyl Methacrylate Tank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -299,7 +299,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://ericturner.dev/posts/cost-of-home-ownership/</t>
+          <t>https://www.science.org/content/blog-post/methyl-methacrylate-tank</t>
         </is>
       </c>
     </row>
@@ -311,7 +311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>That Methyl Methacrylate Tank</t>
+          <t>The real cost of owning a home</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -336,7 +336,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.science.org/content/blog-post/methyl-methacrylate-tank</t>
+          <t>https://ericturner.dev/posts/cost-of-home-ownership/</t>
         </is>
       </c>
     </row>
@@ -385,7 +385,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DynIP – Dynamic DNS with RFC 2136, IPv6, DNSSEC, and BYOD</t>
+          <t>Cloudflare Flagship</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -410,7 +410,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://dynip.dev/</t>
+          <t>https://developers.cloudflare.com/flagship/</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cloudflare Flagship</t>
+          <t>DynIP – Dynamic DNS with RFC 2136, IPv6, DNSSEC, and BYOD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://developers.cloudflare.com/flagship/</t>
+          <t>https://dynip.dev/</t>
         </is>
       </c>
     </row>
@@ -755,32 +755,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OpenRouter, an Exchange for A.I. Models, Raises $113 Million</t>
+          <t>Pope Leo’s A.I. Vision Might Not Be Strange Enough</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/business/dealbook/openrouter-ai-models-fundraising.html</t>
+          <t>https://www.nytimes.com/2026/05/27/opinion/pope-leo-ai-encyclical.html</t>
         </is>
       </c>
     </row>
@@ -792,17 +792,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Two Issues That Could Swing This District</t>
+          <t>OpenRouter, an Exchange for A.I. Models, Raises $113 Million</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/us/100000010903992/ai-data-center-ice-detention-center-arizona.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/dealbook/openrouter-ai-models-fundraising.html</t>
         </is>
       </c>
     </row>
@@ -829,17 +829,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Vatican Takes on Silicon Valley With an A.I. Warning</t>
+          <t>The Two Issues That Could Swing This District</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/business/dealbook/vatican-ai-silicon-valley.html</t>
+          <t>https://www.nytimes.com/video/us/100000010903992/ai-data-center-ice-detention-center-arizona.html</t>
         </is>
       </c>
     </row>
@@ -866,17 +866,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Spencer Pratt Wants to Be Mayor. His Fans Want Him to Be Batman.</t>
+          <t>The Vatican Takes on Silicon Valley With an A.I. Warning</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/27/magazine/spencer-pratt-batman-ads-mayor.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/dealbook/vatican-ai-silicon-valley.html</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Floods Court Dockets with Home-Brewed Lawsuits</t>
+          <t>Spencer Pratt Wants to Be Mayor. His Fans Want Him to Be Batman.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/25/us/politics/artificial-intelliegence-courts.html</t>
+          <t>https://www.nytimes.com/2026/05/27/magazine/spencer-pratt-batman-ads-mayor.html</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Global Oil Price Rises After U.S. Strikes in Iran Cloud Peace Deal</t>
+          <t>KFF’s Chief Executive to Retire</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/business/oil-gas-price-iran.html</t>
+          <t>https://www.nytimes.com/2026/05/27/business/media/kff-drew-altman.html</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SpaceX IPO Filing Reveals Favorable Terms for Elon Musk</t>
+          <t>Artificial Intelligence Floods Court Dockets with Home-Brewed Lawsuits</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/technology/spacex-elon-musk-pay-board-governance.html</t>
+          <t>https://www.nytimes.com/2026/05/25/us/politics/artificial-intelliegence-courts.html</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Teachers Union Urges Schools to Curb A.I. Chatbots and Screen Time</t>
+          <t>Global Oil Price Rises After U.S. Strikes in Iran Cloud Peace Deal</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/27/technology/ai-screens-schools-weingarten.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/oil-gas-price-iran.html</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>At the A.I. Epicenter, Technologists Dismiss Pope Leo’s Warnings About the New Technology</t>
+          <t>SpaceX IPO Filing Reveals Favorable Terms for Elon Musk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/technology/pope-leo-ai-religion.html</t>
+          <t>https://www.nytimes.com/2026/05/26/technology/spacex-elon-musk-pay-board-governance.html</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Writing Is Fundamental to How We Think</t>
+          <t>A.I. Money From I.P.O.s Will Change Philanthropy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/27/opinion/writing-creativity-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/27/opinion/ai-philanthropy-charity.html</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>E.P.A. to Repeal Some Limits on ‘Forever Chemicals’ in Drinking Water</t>
+          <t>Writing Is Fundamental to How We Think</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/18/climate/epa-forever-chemicals-pfas-drinking-water.html</t>
+          <t>https://www.nytimes.com/2026/05/27/opinion/writing-creativity-ai.html</t>
         </is>
       </c>
     </row>
@@ -1199,22 +1199,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>As a Doctor, I Can Understand the Allure of ChatGPT</t>
+          <t>E.P.A. to Repeal Some Limits on ‘Forever Chemicals’ in Drinking Water</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/24/opinion/doctor-ai-chatgpt.html</t>
+          <t>https://www.nytimes.com/2026/05/18/climate/epa-forever-chemicals-pfas-drinking-water.html</t>
         </is>
       </c>
     </row>
@@ -1310,17 +1310,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
+          <t>At the A.I. Epicenter, Technologists Dismiss Pope Leo’s Warnings About the New Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
+          <t>https://www.nytimes.com/2026/05/26/technology/pope-leo-ai-religion.html</t>
         </is>
       </c>
     </row>
@@ -1347,32 +1347,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
+          <t>Trump Eases Restrictions on Climate ‘Super Pollutants’</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NYT · Sunday Opinion</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sunday Opinion</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
+          <t>https://www.nytimes.com/2026/05/21/climate/trump-super-pollutants-hfc-epa-climate-change.html</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>How Cannes Is Grappling With Changes</t>
+          <t>Musk’s SpaceX Goals Shift Ahead of Its I.P.O.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/movies/100000010860400/alissa-reviews-cannes.html</t>
+          <t>https://www.nytimes.com/2026/04/22/technology/elon-musk-spacex-ipo-goals.html</t>
         </is>
       </c>
     </row>
@@ -52473,7 +52473,1376 @@
         </is>
       </c>
     </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Motorola announces a partnership with GrapheneOS</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>https://motorolanews.com/motorola-three-new-b2b-solutions-at-mwc-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>Meta’s AI smart glasses and data privacy concerns</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>https://www.svd.se/a/K8nrV4/metas-ai-smart-glasses-and-data-privacy-concerns-workers-say-we-see-everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>“Microslop” filtered in the official Microsoft Copilot Discord server</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>https://www.windowslatest.com/2026/03/02/microsoft-gets-tired-of-microslop-bans-the-word-on-its-discord-then-locks-the-server-after-backlash/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>British Columbia is permanently adopting daylight time</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>https://www.cbc.ca/news/canada/british-columbia/b-c-adopting-year-round-daylight-time-9.7111657</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>How to talk to anyone and why you should</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/lifeandstyle/2026/feb/24/stranger-secret-how-to-talk-to-anyone-why-you-should</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>/e/OS is a complete, fully “deGoogled” mobile ecosystem</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>https://e.foundation/e-os/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Ars Technica fires reporter after AI controversy involving fabricated quotes</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>https://futurism.com/artificial-intelligence/ars-technica-fires-reporter-ai-quotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Show HN: I built a sub-500ms latency voice agent from scratch</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>https://www.ntik.me/posts/voice-agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Jolla phone – a full-stack European alternative</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>https://commerce.jolla.com/products/jolla-phone-sept-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>New iPad Air, powered by M4</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1427" t="inlineStr">
+        <is>
+          <t>https://www.apple.com/newsroom/2026/03/apple-introduces-the-new-ipad-air-powered-by-m4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Anthropic Cowork feature creates 10GB VM bundle on macOS without warning</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1428" t="inlineStr">
+        <is>
+          <t>https://github.com/anthropics/claude-code/issues/22543</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>U.S. science agency moves to restrict foreign scientists from its labs</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>https://www.science.org/content/article/nist-moves-restrict-foreign-scientists-its-labs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>First in-utero stem cell therapy for fetal spina bifida repair is safe: study</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>https://health.ucdavis.edu/news/headlines/first-ever-in-utero-stem-cell-therapy-for-fetal-spina-bifida-repair-is-safe-study-finds/2026/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Welcome (back) to Macintosh</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>https://take.surf/2026/03/01/welcome-back-to-macintosh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>iPhone 17e</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>https://www.apple.com/newsroom/2026/03/apple-introduces-iphone-17e/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Payphone Go</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>https://walzr.com/payphone-go/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Live Nation Accused of Hurting Music Fans as Antitrust Trial Begins</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/arts/music/live-nation-antitrust-trial.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>Big Lenders’ Risky Loans Are Rattling Wall Street</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/business/private-credit-crisis-blue-owl-capital.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>Iran’s Strategy: Expand the War, Increase the Cost, Outlast Trump</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/world/europe/iran-war-strategy-trump-israel.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>MrBeast Is Getting Into Financial Services. Parents Should Pay Attention.</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/business/mrbeast-step-banking-crypto.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>Who Could Profit From an Energy Crisis?</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/climate/iran-energy-crisis-climate.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>Congestion Pricing Wins in Court After Lengthy Battle With Trump</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1439" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/nyregion/nyc-congestion-pricing-ruling.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>Trump Lays Out His ‘Worst Case’ Scenario in Iran</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>NYT · Politics</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1440" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/us/politics/trump-iran-leaders.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>OpenAI Amends A.I. Deal With the Pentagon</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>NYT · Technology</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/02/technology/openai-pentagon-deal-amended-surveillance.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Tariffs Confound Small Businesses Again</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>NYT · Economy</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/business/economy/tariffs-small-business-confusion-refunds.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>Noem Defends Describing Minneapolis Protesters’ Actions as Domestic Terrorism</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>NYT · Politics</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/us/politics/kristi-noem-senate-hearing.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>Supreme Court Sides With Religious Parents, Blocking California’s Trans Student Policy</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>NYT · Politics</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>Politics</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/02/us/politics/supreme-court-california-trans-students.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>Oil and Natural Gas Prices Keep Climbing as Iran Attacks Escalate</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/business/energy-environment/oil-natural-gas-iran-israel-united-states.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>U.S. Automakers Risk Being Reduced to Niche Producers of Gas Vehicles</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>NYT · Business</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/business/ford-gm-ev-self-driving-cars-china.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>Potomac River Reopens to Some Recreation After Sewer Collapse</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>NYT · Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>Energy &amp; Environment</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/climate/potomac-river-reopens-sewer-collapse.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>Crockett vs. Talarico. Progressive vs. Moderate. Right?</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/upshot/crockett-talarico-texas-senate-election.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>Mamdani’s Parks Dept. Aims to Offer More Recreation With Smaller Budget</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/nyregion/affordable-gyms-new-york.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>Offering Warmth and Care to Homeless People, as Cold Deaths Mount</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/nyregion/nyc-homeless-cold-medical-services.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>Get a Dog, Live Longer?</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/well/pet-longevity-health-benefits.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>Why Does Drinking Mess With My Emotions?</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/03/well/mind/alcohol-emotions-hangovers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>In Dimes Square, a Party Where Toothpicks Were Crucial</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>NYT · U.S.</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>U.S.</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G1453" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/03/02/t-magazine/eel-bar-party-pintxos.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>View Rama's recent LinkedIn activity</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="F1454" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1454" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ramar/recent-activity/all/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1417"/>
+  <autoFilter ref="A1:G1454"/>
 </worksheet>
 </file>
--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -2198,32 +2198,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OpenRouter, an Exchange for A.I. Models, Raises $113 Million</t>
+          <t>Pope Leo’s A.I. Vision Might Not Be Strange Enough</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/business/dealbook/openrouter-ai-models-fundraising.html</t>
+          <t>https://www.nytimes.com/2026/05/27/opinion/pope-leo-ai-encyclical.html</t>
         </is>
       </c>
     </row>
@@ -2235,17 +2235,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Floods Court Dockets with Home-Brewed Lawsuits</t>
+          <t>OpenRouter, an Exchange for A.I. Models, Raises $113 Million</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/25/us/politics/artificial-intelliegence-courts.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/dealbook/openrouter-ai-models-fundraising.html</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Two Issues That Could Swing This District</t>
+          <t>Artificial Intelligence Floods Court Dockets with Home-Brewed Lawsuits</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/video/us/100000010903992/ai-data-center-ice-detention-center-arizona.html</t>
+          <t>https://www.nytimes.com/2026/05/25/us/politics/artificial-intelliegence-courts.html</t>
         </is>
       </c>
     </row>
@@ -2309,17 +2309,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Vatican Takes on Silicon Valley With an A.I. Warning</t>
+          <t>The Two Issues That Could Swing This District</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/business/dealbook/vatican-ai-silicon-valley.html</t>
+          <t>https://www.nytimes.com/video/us/100000010903992/ai-data-center-ice-detention-center-arizona.html</t>
         </is>
       </c>
     </row>
@@ -2346,17 +2346,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Spencer Pratt Wants to Be Mayor. His Fans Want Him to Be Batman.</t>
+          <t>The Vatican Takes on Silicon Valley With an A.I. Warning</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/27/magazine/spencer-pratt-batman-ads-mayor.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/dealbook/vatican-ai-silicon-valley.html</t>
         </is>
       </c>
     </row>
@@ -2383,17 +2383,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KFF’s Chief Executive to Retire</t>
+          <t>Spencer Pratt Wants to Be Mayor. His Fans Want Him to Be Batman.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/27/business/media/kff-drew-altman.html</t>
+          <t>https://www.nytimes.com/2026/05/27/magazine/spencer-pratt-batman-ads-mayor.html</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Global Oil Price Rises After U.S. Strikes in Iran Cloud Peace Deal</t>
+          <t>KFF’s Chief Executive to Retire</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/business/oil-gas-price-iran.html</t>
+          <t>https://www.nytimes.com/2026/05/27/business/media/kff-drew-altman.html</t>
         </is>
       </c>
     </row>
@@ -2457,17 +2457,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SpaceX IPO Filing Reveals Favorable Terms for Elon Musk</t>
+          <t>Global Oil Price Rises After U.S. Strikes in Iran Cloud Peace Deal</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/technology/spacex-elon-musk-pay-board-governance.html</t>
+          <t>https://www.nytimes.com/2026/05/26/business/oil-gas-price-iran.html</t>
         </is>
       </c>
     </row>
@@ -2494,32 +2494,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
+          <t>SpaceX IPO Filing Reveals Favorable Terms for Elon Musk</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NYT · Sunday Opinion</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sunday Opinion</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
+          <t>https://www.nytimes.com/2026/05/26/technology/spacex-elon-musk-pay-board-governance.html</t>
         </is>
       </c>
     </row>
@@ -2531,17 +2531,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Progressives Are Listening to the Wrong People on A.I.</t>
+          <t>What A.I. Philanthropists Can Learn From the Gilded Age</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Sunday Opinion</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Sunday Opinion</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/26/opinion/progressives-left-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/23/opinion/artificial-intelligence-philanthropy-beauty.html</t>
         </is>
       </c>
     </row>
@@ -2568,32 +2568,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>As A.I. Fever Rises in Silicon Valley, Pope Leo Has a Few Words</t>
+          <t>Progressives Are Listening to the Wrong People on A.I.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/25/technology/pope-ai-silicon-valley.html</t>
+          <t>https://www.nytimes.com/2026/05/26/opinion/progressives-left-ai.html</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A.I. Money From I.P.O.s Will Change Philanthropy</t>
+          <t>As A.I. Fever Rises in Silicon Valley, Pope Leo Has a Few Words</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2620,17 +2620,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/27/opinion/ai-philanthropy-charity.html</t>
+          <t>https://www.nytimes.com/2026/05/25/technology/pope-ai-silicon-valley.html</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Writing Is Fundamental to How We Think</t>
+          <t>A.I. Money From I.P.O.s Will Change Philanthropy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/27/opinion/writing-creativity-ai.html</t>
+          <t>https://www.nytimes.com/2026/05/27/opinion/ai-philanthropy-charity.html</t>
         </is>
       </c>
     </row>

--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -11633,17 +11633,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>NextEra Energy to Acquire Dominion, Creating a Utility Giant</t>
+          <t>OpenAI Bought Company That Offered A.I. Tools for Cloning Voices</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -11653,12 +11653,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/business/nextera-dominion-deal.html</t>
+          <t>https://www.nytimes.com/2026/05/15/technology/openai-weightsgg-voice-cloning.html</t>
         </is>
       </c>
     </row>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>For Trump, Soaring Prices Test Voters’ Finances and Patience</t>
+          <t>NextEra Energy to Acquire Dominion, Creating a Utility Giant</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/business/for-trump-soaring-prices-test-voters-finances-and-patience.html</t>
+          <t>https://www.nytimes.com/2026/05/17/business/nextera-dominion-deal.html</t>
         </is>
       </c>
     </row>
@@ -11707,17 +11707,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>How a Secretive Firm Tried (and Failed) to Fix an Epstein Friend’s Tattered Image</t>
+          <t>For Trump, Soaring Prices Test Voters’ Finances and Patience</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/us/politics/epstein-reummler-reputation-management.html</t>
+          <t>https://www.nytimes.com/2026/05/17/business/for-trump-soaring-prices-test-voters-finances-and-patience.html</t>
         </is>
       </c>
     </row>
@@ -11744,22 +11744,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>What A.I. Did to My College Class</t>
+          <t>How a Secretive Firm Tried (and Failed) to Fix an Epstein Friend’s Tattered Image</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/opinion/chatgpt-ai-college-school-graduation.html</t>
+          <t>https://www.nytimes.com/2026/05/17/us/politics/epstein-reummler-reputation-management.html</t>
         </is>
       </c>
     </row>
@@ -11781,17 +11781,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>The Quest for an Elusive Clean Fuel Is Moving Underground</t>
+          <t>It’s Not Just U.S. Stocks. A.I. and Oil Are Moving Global Markets, Too.</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/climate/geologic-hydrogen-clean-energy-underground.html</t>
+          <t>https://www.nytimes.com/2026/05/15/business/chip-ai-oil-emerging-stock-markets.html</t>
         </is>
       </c>
     </row>
@@ -11818,17 +11818,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>W.H.O. Declares Ebola Outbreak a Global Health Emergency</t>
+          <t>The Stock Market’s Winning Streak Is About to Be Tested</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/world/africa/ebola-congo-uganda-who-public-health-emergency.html</t>
+          <t>https://www.nytimes.com/2026/05/15/business/stocks-bonds-interest-rates-inflation.html</t>
         </is>
       </c>
     </row>
@@ -11855,22 +11855,22 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>To Critics, Trump Remarks Reveal a Billionaire Out of Touch</t>
+          <t>What A.I. Did to My College Class</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/us/politics/trump-billionaire-iran-war-cost.html</t>
+          <t>https://www.nytimes.com/2026/05/17/opinion/chatgpt-ai-college-school-graduation.html</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>7 Republicans Voted to Convict Trump. Most Are No Longer in Office.</t>
+          <t>On Capitol Hill, a Sexual Harassment ‘Minefield’ Persists</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/16/us/politics/republicans-trump-cassidy-conviction-impeachment.html</t>
+          <t>https://www.nytimes.com/2026/05/16/us/politics/on-capitol-hill-a-sexual-harassment-minefield-persists.html</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>After a Rough Start, Mamdani Focuses on Skeptical Black New Yorkers</t>
+          <t>A.I. Safety Is So Back + Mythos Mayhem with Nikesh Arora + Hot Mess Express</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/nyregion/mamdani-black-voters-nyc.html</t>
+          <t>https://www.nytimes.com/2026/05/15/podcasts/ai-safety-is-so-back-mythos-mayhem-with-nikesh-arora-hot-mess-express.html</t>
         </is>
       </c>
     </row>
@@ -11966,32 +11966,32 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>We Are Sliding Back Into the Middle Ages</t>
+          <t>Trump Calls Xi a ‘Friend.’ But He Left China Without Any Breakthroughs.</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · U.S.</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>U.S.</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/opinion/supernatural-religion-reality.html</t>
+          <t>https://www.nytimes.com/2026/05/16/world/europe/trump-xi-china-summit.html</t>
         </is>
       </c>
     </row>
@@ -12003,17 +12003,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Shoppers’ Frenzy for ‘Royal Pop’ Pocket Watches Forces Swatch to Shut Stores</t>
+          <t>How a ‘Model’ for Climate Migration Became a Cautionary Tale</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -12023,12 +12023,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/16/business/swatch-audemars-piguet-watch-launch-closures.html</t>
+          <t>https://www.nytimes.com/2026/05/16/climate/isle-jean-charles-relocation.html</t>
         </is>
       </c>
     </row>
@@ -12040,17 +12040,17 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Bulgaria Wins Eurovision Song Contest as Israel Takes Second</t>
+          <t>OpenAI and Khan Academy Made a Chatbot. What Can We Learn?</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/16/arts/music/dara-bulgaria-bangaranga-eurovision-winner.html</t>
+          <t>https://www.nytimes.com/2026/05/16/business/tyrangiel-ai-book-openai-khan-academy-khanmigo.html</t>
         </is>
       </c>
     </row>
@@ -12077,17 +12077,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>A Newspaper’s Birches Bend and Occasionally Break</t>
+          <t>The Quest for an Elusive Clean Fuel Is Moving Underground</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/insider/birch-trees-new-york-times-building.html</t>
+          <t>https://www.nytimes.com/2026/05/17/climate/geologic-hydrogen-clean-energy-underground.html</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Why Neutral Maps Could Empower Black Voters as Much as the Voting Rights Act</t>
+          <t>How a Nature Cruise Turned Into a Nightmare</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -12134,12 +12134,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/upshot/redistricting-race-court-gerrymanders-elections.html</t>
+          <t>https://www.nytimes.com/2026/05/16/world/europe/hantavirus-hondius-cruise.html</t>
         </is>
       </c>
     </row>
@@ -12151,17 +12151,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Stereotypically Antisocial Pets</t>
+          <t>OpenAI Considers Legal Action Against Apple in Strained Relationship</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -12171,12 +12171,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/crosswords/daily-puzzle-2026-05-18.html</t>
+          <t>https://www.nytimes.com/2026/05/14/technology/openai-apple-legal-action.html</t>
         </is>
       </c>
     </row>
@@ -12188,17 +12188,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>The Iran War Is Crippling One of the World’s Wealthiest Nations</t>
+          <t>A Stolen Charity or Sour Grapes? Musk’s OpenAI Suit Is in Jury’s Hands.</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>NYT · Business</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -12208,12 +12208,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/business/qatar-economy-iran-war.html</t>
+          <t>https://www.nytimes.com/2026/05/14/technology/openai-trial-elon-musk-sam-altman.html</t>
         </is>
       </c>
     </row>
@@ -12225,32 +12225,32 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Trump and Xi Would Need Personality Transplants to Get This Deal Done</t>
+          <t>Nvidia’s Future in China Remains Unclear After Trump-Xi Summit</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/opinion/trump-china-xi-trade.html</t>
+          <t>https://www.nytimes.com/2026/05/15/business/nvidia-china-chips.html</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Corrections: May 17, 2026</t>
+          <t>After a Rough Start, Mamdani Focuses on Skeptical Black New Yorkers</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/pageoneplus/corrections-may-17-2026.html</t>
+          <t>https://www.nytimes.com/2026/05/17/nyregion/mamdani-black-voters-nyc.html</t>
         </is>
       </c>
     </row>
@@ -12299,32 +12299,32 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>The Value in Recording Hard Conversations</t>
+          <t>The Revolt Against the Girl Bosses Has Finally Come</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/briefing/the-value-in-recording-hard-conversations.html</t>
+          <t>https://www.nytimes.com/2026/05/15/opinion/reese-witherspoon-mel-robbins-girlboss-ai.html</t>
         </is>
       </c>
     </row>
@@ -12336,32 +12336,32 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Spelling Bee Forum</t>
+          <t>What A.I. Kant Do</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>NYT · U.S.</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>U.S.</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/05/17/crosswords/spelling-bee-forum.html</t>
+          <t>https://www.nytimes.com/2026/05/16/opinion/ai-liberal-arts.html</t>
         </is>
       </c>
     </row>

--- a/data/digest_archives/dd_archive.xlsx
+++ b/data/digest_archives/dd_archive.xlsx
@@ -200,7 +200,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mechanical Watch (2022)</t>
+          <t>GrapheneOS has been ported to Android 17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -225,7 +225,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://ciechanow.ski/mechanical-watch/</t>
+          <t>https://discuss.grapheneos.org/d/36469-grapheneos-has-been-ported-to-android-17-and-official-releases-are-coming-soon</t>
         </is>
       </c>
     </row>
@@ -274,7 +274,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Feds freaked over Fable 5 after 'fix this code', not jailbreak, say researchers</t>
+          <t>Mechanical Watch (2022)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -299,7 +299,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/06/15/feds-freaked-over-fable-5-after-simple-fix-this-code-prompt-not-jailbreak-says-researcher/5255827</t>
+          <t>https://ciechanow.ski/mechanical-watch/</t>
         </is>
       </c>
     </row>
@@ -311,7 +311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GrapheneOS has been ported to Android 17</t>
+          <t>Is Meta destroying its engineering organization?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -336,7 +336,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://discuss.grapheneos.org/d/36469-grapheneos-has-been-ported-to-android-17-and-official-releases-are-coming-soon</t>
+          <t>https://newsletter.pragmaticengineer.com/p/why-is-meta-destroying-its-engineering</t>
         </is>
       </c>
     </row>
@@ -348,7 +348,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The time the x86 emulator team found code so bad they fixed it during emulation</t>
+          <t>Feds freaked over Fable 5 after 'fix this code', not jailbreak, say researchers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -373,7 +373,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://devblogs.microsoft.com/oldnewthing/20260615-00/?p=112419</t>
+          <t>https://www.theregister.com/security/2026/06/15/feds-freaked-over-fable-5-after-simple-fix-this-code-prompt-not-jailbreak-says-researcher/5255827</t>
         </is>
       </c>
     </row>
@@ -385,7 +385,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Is Meta destroying its engineering organization?</t>
+          <t>Apple is about to make Hide My Email useless</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -410,7 +410,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://newsletter.pragmaticengineer.com/p/why-is-meta-destroying-its-engineering</t>
+          <t>https://arseniyshestakov.com/2026/06/16/apple-is-about-to-make-hide-my-email-useless/</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Apple is about to make Hide My Email useless</t>
+          <t>The time the x86 emulator team found code so bad they fixed it during emulation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://arseniyshestakov.com/2026/06/16/apple-is-about-to-make-hide-my-email-useless/</t>
+          <t>https://devblogs.microsoft.com/oldnewthing/20260615-00/?p=112419</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U.S. pulling ocean sensors a 'shock' for Canadian research as El Niño nears</t>
+          <t>Calvin and Hobbes and the price of integrity</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.timescolonist.com/local-news/us-pulling-ocean-sensors-a-shock-for-canadian-research-as-el-nino-nears-12422874</t>
+          <t>https://therepublicofletters.substack.com/p/calvin-and-hobbes-and-the-price-of</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Calvin and Hobbes and the price of integrity</t>
+          <t>TIL: You can make HTTP requests without curl using Bash /dev/TCP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://therepublicofletters.substack.com/p/calvin-and-hobbes-and-the-price-of</t>
+          <t>https://mareksuppa.com/til/bash-dev-tcp-http-without-curl/</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TIL: You can make HTTP requests without curl using Bash /dev/TCP</t>
+          <t>U.S. pulling ocean sensors a 'shock' for Canadian research as El Niño nears</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://mareksuppa.com/til/bash-dev-tcp-http-without-curl/</t>
+          <t>https://www.timescolonist.com/local-news/us-pulling-ocean-sensors-a-shock-for-canadian-research-as-el-nino-nears-12422874</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SpaceX Is Buying Cursor</t>
+          <t>Has AI already killed self-help nonfiction books?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/cvgd5g7d7gyo</t>
+          <t>https://tim.blog/2026/06/12/has-ai-already-killed-nonfiction/</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Big Questions for Warsh as New Era for the Fed Begins</t>
+          <t>The Cloud Has Sound: The Unrelenting and Unseen Cost of the A.I. Boom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/16/business/dealbook/warsh-fed-questions.html</t>
+          <t>https://www.nytimes.com/2026/06/17/us/data-centers-noise-pollution.html</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>How a Deal to End the War in Iran Could Affect Energy Prices</t>
+          <t>Big Questions for Warsh as New Era for the Fed Begins</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/16/climate/iran-war-energy-prices.html</t>
+          <t>https://www.nytimes.com/2026/06/16/business/dealbook/warsh-fed-questions.html</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D.O.J. Seeks to Halt Pollution Lawsuit Against Elon Musk’s Data Center</t>
+          <t>How a Deal to End the War in Iran Could Affect Energy Prices</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/16/climate/xai-musk-mississippi-grok-turbine-lawsuit-naacp.html</t>
+          <t>https://www.nytimes.com/2026/06/16/climate/iran-war-energy-prices.html</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Riding High After I.P.O., SpaceX Will Buy A.I. Start-Up for $60 Billion</t>
+          <t>D.O.J. Seeks to Halt Pollution Lawsuit Against Elon Musk’s Data Center</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/16/business/spacex-cursor-aquisition-ipo.html</t>
+          <t>https://www.nytimes.com/2026/06/16/climate/xai-musk-mississippi-grok-turbine-lawsuit-naacp.html</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Battle With Anthropic Is the Start of a New Kind of Conflict</t>
+          <t>Riding High After I.P.O., SpaceX Will Buy A.I. Start-Up for $60 Billion</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/16/opinion/anthropic-fable-ai-trump-administration.html</t>
+          <t>https://www.nytimes.com/2026/06/16/business/spacex-cursor-aquisition-ipo.html</t>
         </is>
       </c>
     </row>
@@ -866,22 +866,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Iran War is Forcing Energy-Importing Countries to Turn Inward</t>
+          <t>Dear A.I. Companies: The Doom Trolling Needs to Stop</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/08/business/energy-environment/iran-war-energy-oil.html</t>
+          <t>https://www.nytimes.com/2026/06/17/opinion/ai-dangerous-openai-anthropic.html</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>How to Run a News Company in the Age of Polarization and A.I. Slop</t>
+          <t>The Battle With Anthropic Is the Start of a New Kind of Conflict</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -918,17 +918,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/14/business/nbc-news-cesar-conde.html</t>
+          <t>https://www.nytimes.com/2026/06/16/opinion/anthropic-fable-ai-trump-administration.html</t>
         </is>
       </c>
     </row>
@@ -940,17 +940,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A.I. Boom Ignites Asian Chip Companies</t>
+          <t>Who Will Get Spirit Airlines’ Coveted Flights at LaGuardia?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/16/technology/taiwan-south-korea-ai-chips.html</t>
+          <t>https://www.nytimes.com/2026/06/17/business/spirit-airlines-laguardia-airport.html</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Justice Dept. Considering Death Penalty for Alleged National Guard Shooter</t>
+          <t>The Iran War is Forcing Energy-Importing Countries to Turn Inward</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · Energy &amp; Environment</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Energy &amp; Environment</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/16/us/politics/doj-national-guard-shooting.html</t>
+          <t>https://www.nytimes.com/2026/06/08/business/energy-environment/iran-war-energy-oil.html</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>State Attorneys General Are Investigating OpenAI</t>
+          <t>Here’s the latest.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/13/technology/states-investigating-openai.html</t>
+          <t>https://www.nytimes.com/2026/06/16/us/politics/heres-the-latest.html</t>
         </is>
       </c>
     </row>
@@ -1051,22 +1051,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>How to Kick SpaceX Out of Your 401(k)</t>
+          <t>Justice Dept. Considering Death Penalty for Alleged National Guard Shooter</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Politics</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/13/opinion/spacex-stock-ipo-ai.html</t>
+          <t>https://www.nytimes.com/2026/06/16/us/politics/doj-national-guard-shooting.html</t>
         </is>
       </c>
     </row>
@@ -1088,17 +1088,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SpaceX’s Stock Surges on First Full Day of Trading</t>
+          <t>State Attorneys General Are Investigating OpenAI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NYT · AI</t>
+          <t>NYT · Technology</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/15/business/spacex-stock.html</t>
+          <t>https://www.nytimes.com/2026/06/13/technology/states-investigating-openai.html</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Everyone Wants to Tax A.I. The Big Disagreement: How?</t>
+          <t>How to Run a News Company in the Age of Polarization and A.I. Slop</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/13/business/dealbook/ai-tax-proposals.html</t>
+          <t>https://www.nytimes.com/2026/06/14/business/nbc-news-cesar-conde.html</t>
         </is>
       </c>
     </row>
@@ -1162,22 +1162,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gas Prices May Remain High Despite US-Iran Deal</t>
+          <t>How to Kick SpaceX Out of Your 401(k)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NYT · Energy &amp; Environment</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Energy &amp; Environment</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/16/business/energy-environment/us-iran-deal-gas-prices.html</t>
+          <t>https://www.nytimes.com/2026/06/13/opinion/spacex-stock-ipo-ai.html</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trump Breaks Up Education Dept., Prompting Worries Over Civil Rights</t>
+          <t>This Teacher Has Doubts About A.I. But He Won a Prize Using It.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/16/us/politics/education-department-civil-rights-trump.html</t>
+          <t>https://www.nytimes.com/2026/06/17/nyregion/teacher-prize-artificial-intelligence.html</t>
         </is>
       </c>
     </row>
@@ -1236,17 +1236,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Trump Administration Reignites Its Feud With Anthropic Over Latest A.I. Models</t>
+          <t>Everyone Wants to Tax A.I. The Big Disagreement: How?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/13/us/politics/trump-anthropic-ai-models.html</t>
+          <t>https://www.nytimes.com/2026/06/13/business/dealbook/ai-tax-proposals.html</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Google Sues to Stop Chinese Cybercrime Group from Using Its A.I.</t>
+          <t>The U.S. Economy Is Leaving Small Businesses Behind</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NYT · Technology</t>
+          <t>NYT · Economy</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/12/technology/google-lawsuit-china-ai-scams.html</t>
+          <t>https://www.nytimes.com/2026/06/17/business/economy/small-business-strain-economy.html</t>
         </is>
       </c>
     </row>
@@ -1310,17 +1310,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Obama’s Nuclear Deal Looms Over Trump’s Iran Negotiations</t>
+          <t>The Battle Over A.I. in the Classroom</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NYT · Politics</t>
+          <t>NYT · AI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/16/us/politics/obama-nuclear-deal-trump-iran.html</t>
+          <t>https://www.nytimes.com/2026/06/17/podcasts/the-daily/battle-over-ai-in-school.html</t>
         </is>
       </c>
     </row>
@@ -1347,32 +1347,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Good Luck, Kevin Warsh. You’ll Need It.</t>
+          <t>Wages Are Falling. Wealth Is Surging. No Wonder Americans Are Unhappy.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NYT · Opinion</t>
+          <t>NYT · Business</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>news</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/16/opinion/kevin-warsh-fed-chair-interest-rates-trump.html</t>
+          <t>https://www.nytimes.com/2026/06/13/business/economy-trillionaire-wealth-wages.html</t>
         </is>
       </c>
     </row>
@@ -1384,17 +1384,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Turning to ChatGPT for Help Instead of Your Doctor</t>
+          <t>Good Luck, Kevin Warsh. You’ll Need It.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NYT · Sunday Opinion</t>
+          <t>NYT · Opinion</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sunday Opinion</t>
+          <t>Opinion</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/06/13/opinion/doctor-chatgpt.html</t>
+          <t>https://www.nytimes.com/2026/06/16/opinion/kevin-warsh-fed-chair-interest-rates-trump.html</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Policy Updates</t>
+          <t>Pro Tip - Reset your usage limits on your schedule</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/ClaudeAI/comments/1u7hoxg/policy_updates/</t>
+          <t>https://www.reddit.com/r/ClaudeAI/comments/1u7i5ow/pro_tip_reset_your_usage_limits_on_your_schedule/</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pro Tip - Reset your usage limits on your schedule</t>
+          <t>I see the full picture now!</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/ClaudeAI/comments/1u7i5ow/pro_tip_reset_your_usage_limits_on_your_schedule/</t>
+          <t>https://www.reddit.com/r/ClaudeAI/comments/1u7gl55/i_see_the_full_picture_now/</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>I see the full picture now!</t>
+          <t>Policy Updates</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/ClaudeAI/comments/1u7gl55/i_see_the_full_picture_now/</t>
+          <t>https://www.reddit.com/r/ClaudeAI/comments/1u7hoxg/policy_updates/</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Is there any way to hide the Fable 5 notification?</t>
+          <t>Fable 5 being gone made me realize how hard it is to go back</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/ClaudeAI/comments/1u6zp8p/is_there_any_way_to_hide_the_fable_5_notification/</t>
+          <t>https://www.reddit.com/r/ClaudeAI/comments/1u7cifh/fable_5_being_gone_made_me_realize_how_hard_it_is/</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fable 5 being gone made me realize how hard it is to go back</t>
+          <t>Is there any way to hide the Fable 5 notification?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/ClaudeAI/comments/1u7cifh/fable_5_being_gone_made_me_realize_how_hard_it_is/</t>
+          <t>https://www.reddit.com/r/ClaudeAI/comments/1u6zp8p/is_there_any_way_to_hide_the_fable_5_notification/</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trump official says it's "up to Anthropic" as to whether or not a resolution is found quickly in the Mythos/Fable shutdown.</t>
+          <t>Been Using Sonnet 4.6 on medium effort and cant understand why people are using larger models at all?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/ClaudeAI/comments/1u73kmd/trump_official_says_its_up_to_anthropic_as_to/</t>
+          <t>https://www.reddit.com/r/ClaudeAI/comments/1u7l40n/been_using_sonnet_46_on_medium_effort_and_cant/</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Been Using Sonnet 4.6 on medium effort and cant understand why people are using larger models at all?</t>
+          <t>Trump official says it's "up to Anthropic" as to whether or not a resolution is found quickly in the Mythos/Fable shutdown.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/ClaudeAI/comments/1u7l40n/been_using_sonnet_46_on_medium_effort_and_cant/</t>
+          <t>https://www.reddit.com/r/ClaudeAI/comments/1u73kmd/trump_official_says_its_up_to_anthropic_as_to/</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Feds freaked over Fable 5 after simple 'fix this code' prompt, not jailbreak, says researcher</t>
+          <t>Anthropic just published data from 400k Claude Code sessions, and the headline buries the real story: your CS degree is becoming optional</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/ClaudeCode/comments/1u7hmvw/feds_freaked_over_fable_5_after_simple_fix_this/</t>
+          <t>https://www.reddit.com/r/ClaudeCode/comments/1u7u8up/anthropic_just_published_data_from_400k_claude/</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Anthropic just published data from 400k Claude Code sessions, and the headline buries the real story: your CS degree is becoming optional</t>
+          <t>Feds freaked over Fable 5 after simple 'fix this code' prompt, not jailbreak, says researcher</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/ClaudeCode/comments/1u7u8up/anthropic_just_published_data_from_400k_claude/</t>
+          <t>https://www.reddit.com/r/ClaudeCode/comments/1u7hmvw/feds_freaked_over_fable_5_after_simple_fix_this/</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>iPhone Shortcut to Append to Daily Note</t>
+          <t>Showcase as a law student</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/ObsidianMD/comments/1u73sn7/iphone_shortcut_to_append_to_daily_note/</t>
+          <t>https://www.reddit.com/r/ObsidianMD/comments/1u7u7is/showcase_as_a_law_student/</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Showcase as a law student</t>
+          <t>iPhone Shortcut to Append to Daily Note</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/ObsidianMD/comments/1u7u7is/showcase_as_a_law_student/</t>
+          <t>https://www.reddit.com/r/ObsidianMD/comments/1u73sn7/iphone_shortcut_to_append_to_daily_note/</t>
         </is>
       </c>
     </row>
